--- a/dev_docs/Tetra数值表_26_7_21.xlsx
+++ b/dev_docs/Tetra数值表_26_7_21.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\12044\AppData\Roaming\PrismLauncher\instances\SDBF\minecraft\dev_docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04AB5BC9-2463-4BCD-B47A-67B394FF691D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E01592-51F0-48CD-9331-CE5E5603FBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="材料" sheetId="1" r:id="rId1"/>
@@ -19,23 +19,12 @@
     <sheet name="SA" sheetId="2" r:id="rId4"/>
     <sheet name="护甲" sheetId="3" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="541">
   <si>
     <t>刀刃</t>
   </si>
@@ -1323,10 +1312,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>通量注入3k2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>'#forge:ingots/regalium'</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1861,10 +1846,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>暴击率+0.07</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>经验获取+0.</t>
     </r>
@@ -2175,6 +2156,226 @@
   <si>
     <t>火焰伤害+4</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>古代灵魂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>土星环合金锭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙锭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>压缩铁锭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>塑料片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遗弃青铜锭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硅岩锭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>压实耀魂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硅岩铁合金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器级硅岩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凯金锭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合一碎片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞龙核心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级控制水晶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>补天合金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大型控制水晶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神龙核心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>混沌核心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.3.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.3.6</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.3.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.3.8</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.3.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>托林纤维</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强韧神经腺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨铁锭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>氮质体膜片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星浆晶体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.1.3</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰晶合金锭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰坦二型锭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>epsilon尘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红移之熵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不融冰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>风暴氢晶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神门残片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.1.4</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜伤害+30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>癫火抗性+0.03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2743,18 +2944,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X163"/>
-  <sheetFormatPr defaultColWidth="16.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:X170"/>
+  <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="8.6640625" style="3" customWidth="1"/>
-    <col min="4" max="5" width="16.6640625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" style="3" customWidth="1"/>
-    <col min="7" max="16" width="12.6640625" style="3" customWidth="1"/>
-    <col min="17" max="19" width="15.6640625" style="3" customWidth="1"/>
-    <col min="20" max="16384" width="16.6640625" style="3"/>
+    <col min="1" max="3" width="8.625" style="3" customWidth="1"/>
+    <col min="4" max="5" width="16.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.625" style="3" customWidth="1"/>
+    <col min="7" max="16" width="12.625" style="3" customWidth="1"/>
+    <col min="17" max="19" width="15.625" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="16.625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2771,10 +2972,10 @@
         <v>4</v>
       </c>
       <c r="J1" s="24" t="s">
+        <v>364</v>
+      </c>
+      <c r="K1" s="24" t="s">
         <v>365</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>366</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>5</v>
@@ -2802,7 +3003,7 @@
       </c>
       <c r="V1" s="34"/>
     </row>
-    <row r="2" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
@@ -2855,13 +3056,13 @@
         <v>318</v>
       </c>
       <c r="U2" s="34" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="V2" s="34"/>
       <c r="W2" s="34"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
@@ -2914,7 +3115,7 @@
       <c r="W3" s="35"/>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
@@ -2950,13 +3151,13 @@
         <v>14</v>
       </c>
       <c r="U4" s="24" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="V4" s="24" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D5" s="3" t="s">
         <v>15</v>
       </c>
@@ -2980,13 +3181,13 @@
         <v>26</v>
       </c>
       <c r="Q5" s="24" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="R5" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
@@ -3023,7 +3224,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="3" t="s">
         <v>28</v>
       </c>
@@ -3047,16 +3248,16 @@
         <v>0</v>
       </c>
       <c r="P7" s="24" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q7" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="R7" s="24" t="s">
         <v>416</v>
       </c>
-      <c r="R7" s="24" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F8" s="3" t="s">
         <v>29</v>
       </c>
@@ -3067,10 +3268,10 @@
         <v>14</v>
       </c>
       <c r="R8" s="24" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F9" s="3" t="s">
         <v>30</v>
       </c>
@@ -3087,7 +3288,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
@@ -3152,7 +3353,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -3212,7 +3413,7 @@
       <c r="R11" s="9"/>
       <c r="S11" s="9"/>
     </row>
-    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="12" t="s">
         <v>46</v>
       </c>
@@ -3264,7 +3465,7 @@
       <c r="R12" s="9"/>
       <c r="S12" s="9"/>
     </row>
-    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C13" s="12" t="s">
         <v>46</v>
       </c>
@@ -3318,7 +3519,7 @@
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
     </row>
-    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>6</v>
       </c>
@@ -3378,7 +3579,7 @@
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
     </row>
-    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="5" t="s">
         <v>57</v>
       </c>
@@ -3432,7 +3633,7 @@
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
     </row>
-    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>8</v>
       </c>
@@ -3492,7 +3693,7 @@
       <c r="R16" s="9"/>
       <c r="S16" s="9"/>
     </row>
-    <row r="17" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="12" t="s">
         <v>63</v>
       </c>
@@ -3546,7 +3747,7 @@
       <c r="R17" s="9"/>
       <c r="S17" s="9"/>
     </row>
-    <row r="18" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>9</v>
       </c>
@@ -3606,7 +3807,7 @@
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
     </row>
-    <row r="19" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>4</v>
       </c>
@@ -3664,7 +3865,7 @@
       <c r="R19" s="9"/>
       <c r="S19" s="9"/>
     </row>
-    <row r="20" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="12" t="s">
         <v>73</v>
       </c>
@@ -3716,7 +3917,7 @@
       <c r="R20" s="9"/>
       <c r="S20" s="9"/>
     </row>
-    <row r="21" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>5</v>
       </c>
@@ -3769,13 +3970,13 @@
         <v>2</v>
       </c>
       <c r="Q21" s="23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R21" s="9"/>
       <c r="S21" s="9"/>
       <c r="U21" s="24"/>
     </row>
-    <row r="22" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C22" s="5" t="s">
         <v>78</v>
       </c>
@@ -3822,13 +4023,13 @@
         <v>2</v>
       </c>
       <c r="Q22" s="23" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="R22" s="9"/>
       <c r="S22" s="9"/>
       <c r="W22" s="24"/>
     </row>
-    <row r="23" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="5" t="s">
         <v>78</v>
       </c>
@@ -3880,7 +4081,7 @@
       <c r="R23" s="9"/>
       <c r="S23" s="9"/>
     </row>
-    <row r="24" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>6</v>
       </c>
@@ -3940,7 +4141,7 @@
       </c>
       <c r="S24" s="9"/>
     </row>
-    <row r="25" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C25" s="12" t="s">
         <v>83</v>
       </c>
@@ -3993,7 +4194,7 @@
       <c r="S25" s="9"/>
       <c r="U25" s="24"/>
     </row>
-    <row r="26" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C26" s="12" t="s">
         <v>83</v>
       </c>
@@ -4043,12 +4244,12 @@
         <v>90</v>
       </c>
       <c r="R26" s="23" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="S26" s="9"/>
       <c r="U26" s="24"/>
     </row>
-    <row r="27" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>8</v>
       </c>
@@ -4106,7 +4307,7 @@
       <c r="R27" s="9"/>
       <c r="S27" s="9"/>
     </row>
-    <row r="28" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C28" s="5" t="s">
         <v>91</v>
       </c>
@@ -4158,7 +4359,7 @@
       <c r="R28" s="9"/>
       <c r="S28" s="9"/>
     </row>
-    <row r="29" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C29" s="5" t="s">
         <v>91</v>
       </c>
@@ -4210,7 +4411,7 @@
       <c r="R29" s="9"/>
       <c r="S29" s="9"/>
     </row>
-    <row r="30" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>9</v>
       </c>
@@ -4266,12 +4467,12 @@
         <v>98</v>
       </c>
       <c r="R30" s="23" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="S30" s="9"/>
       <c r="U30" s="24"/>
     </row>
-    <row r="31" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C31" s="12" t="s">
         <v>96</v>
       </c>
@@ -4321,12 +4522,12 @@
         <v>85</v>
       </c>
       <c r="R31" s="23" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="S31" s="9"/>
       <c r="U31" s="24"/>
     </row>
-    <row r="32" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>8</v>
       </c>
@@ -4386,7 +4587,7 @@
       <c r="R32" s="9"/>
       <c r="S32" s="9"/>
     </row>
-    <row r="33" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C33" s="5" t="s">
         <v>100</v>
       </c>
@@ -4440,7 +4641,7 @@
       <c r="R33" s="9"/>
       <c r="S33" s="9"/>
     </row>
-    <row r="34" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C34" s="5" t="s">
         <v>100</v>
       </c>
@@ -4489,13 +4690,13 @@
         <v>5</v>
       </c>
       <c r="Q34" s="23" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="R34" s="9"/>
       <c r="S34" s="9"/>
       <c r="U34" s="24"/>
     </row>
-    <row r="35" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>9</v>
       </c>
@@ -4553,12 +4754,12 @@
         <v>112</v>
       </c>
       <c r="R35" s="23" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="S35" s="9"/>
       <c r="U35" s="24"/>
     </row>
-    <row r="36" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C36" s="12" t="s">
         <v>109</v>
       </c>
@@ -4612,7 +4813,7 @@
       <c r="R36" s="9"/>
       <c r="S36" s="9"/>
     </row>
-    <row r="37" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C37" s="12" t="s">
         <v>109</v>
       </c>
@@ -4666,7 +4867,7 @@
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
     </row>
-    <row r="38" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>10</v>
       </c>
@@ -4726,7 +4927,7 @@
       <c r="R38" s="9"/>
       <c r="S38" s="9"/>
     </row>
-    <row r="39" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C39" s="5" t="s">
         <v>119</v>
       </c>
@@ -4780,7 +4981,7 @@
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
     </row>
-    <row r="40" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C40" s="5" t="s">
         <v>119</v>
       </c>
@@ -4829,13 +5030,13 @@
         <v>4</v>
       </c>
       <c r="Q40" s="23" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="R40" s="9"/>
       <c r="S40" s="9"/>
       <c r="U40" s="24"/>
     </row>
-    <row r="41" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>11</v>
       </c>
@@ -4895,7 +5096,7 @@
       <c r="R41" s="9"/>
       <c r="S41" s="9"/>
     </row>
-    <row r="42" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C42" s="12" t="s">
         <v>127</v>
       </c>
@@ -4947,12 +5148,12 @@
         <v>112</v>
       </c>
       <c r="R42" s="23" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S42" s="9"/>
       <c r="U42" s="24"/>
     </row>
-    <row r="43" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>13</v>
       </c>
@@ -5007,13 +5208,13 @@
         <v>5</v>
       </c>
       <c r="Q43" s="23" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="R43" s="9"/>
       <c r="S43" s="9"/>
       <c r="W43" s="24"/>
     </row>
-    <row r="44" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C44" s="5" t="s">
         <v>133</v>
       </c>
@@ -5062,13 +5263,13 @@
         <v>4</v>
       </c>
       <c r="Q44" s="23" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="R44" s="9"/>
       <c r="S44" s="9"/>
       <c r="U44" s="24"/>
     </row>
-    <row r="45" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C45" s="5" t="s">
         <v>133</v>
       </c>
@@ -5122,7 +5323,7 @@
       <c r="R45" s="9"/>
       <c r="S45" s="9"/>
     </row>
-    <row r="46" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C46" s="5" t="s">
         <v>133</v>
       </c>
@@ -5176,7 +5377,7 @@
       <c r="R46" s="9"/>
       <c r="S46" s="9"/>
     </row>
-    <row r="47" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>14</v>
       </c>
@@ -5236,7 +5437,7 @@
       <c r="R47" s="9"/>
       <c r="S47" s="9"/>
     </row>
-    <row r="48" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C48" s="12" t="s">
         <v>143</v>
       </c>
@@ -5285,13 +5486,13 @@
         <v>4</v>
       </c>
       <c r="Q48" s="23" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="R48" s="9"/>
       <c r="S48" s="9"/>
       <c r="U48" s="24"/>
     </row>
-    <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>16</v>
       </c>
@@ -5353,7 +5554,7 @@
       </c>
       <c r="S49" s="9"/>
     </row>
-    <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C50" s="5" t="s">
         <v>149</v>
       </c>
@@ -5409,7 +5610,7 @@
       </c>
       <c r="S50" s="9"/>
     </row>
-    <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C51" s="5" t="s">
         <v>149</v>
       </c>
@@ -5463,7 +5664,7 @@
       <c r="R51" s="9"/>
       <c r="S51" s="9"/>
     </row>
-    <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C52" s="5" t="s">
         <v>149</v>
       </c>
@@ -5517,7 +5718,7 @@
       <c r="R52" s="9"/>
       <c r="S52" s="9"/>
     </row>
-    <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>19</v>
       </c>
@@ -5577,7 +5778,7 @@
       <c r="R53" s="9"/>
       <c r="S53" s="9"/>
     </row>
-    <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C54" s="12" t="s">
         <v>163</v>
       </c>
@@ -5626,13 +5827,13 @@
         <v>5</v>
       </c>
       <c r="Q54" s="23" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="R54" s="9"/>
       <c r="S54" s="9"/>
       <c r="U54" s="24"/>
     </row>
-    <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C55" s="12" t="s">
         <v>163</v>
       </c>
@@ -5688,7 +5889,7 @@
       </c>
       <c r="S55" s="9"/>
     </row>
-    <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C56" s="5" t="s">
         <v>173</v>
       </c>
@@ -5742,7 +5943,7 @@
       <c r="R56" s="9"/>
       <c r="S56" s="9"/>
     </row>
-    <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C57" s="5" t="s">
         <v>173</v>
       </c>
@@ -5794,11 +5995,11 @@
         <v>178</v>
       </c>
       <c r="R57" s="23" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="S57" s="9"/>
     </row>
-    <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>22</v>
       </c>
@@ -5853,17 +6054,17 @@
         <v>6</v>
       </c>
       <c r="Q58" s="23" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="R58" s="9" t="s">
         <v>182</v>
       </c>
       <c r="S58" s="23" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="U58" s="24"/>
     </row>
-    <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>14</v>
       </c>
@@ -5923,7 +6124,7 @@
       <c r="R59" s="9"/>
       <c r="S59" s="9"/>
     </row>
-    <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C60" s="5" t="s">
         <v>186</v>
       </c>
@@ -5979,7 +6180,7 @@
       </c>
       <c r="S60" s="9"/>
     </row>
-    <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>24</v>
       </c>
@@ -6039,7 +6240,7 @@
       <c r="R61" s="9"/>
       <c r="S61" s="9"/>
     </row>
-    <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C62" s="25" t="s">
         <v>288</v>
       </c>
@@ -6096,7 +6297,7 @@
       <c r="S62" s="9"/>
       <c r="U62" s="24"/>
     </row>
-    <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>24</v>
       </c>
@@ -6154,14 +6355,14 @@
         <v>142</v>
       </c>
       <c r="R63" s="23" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="S63" s="23" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="U63" s="24"/>
     </row>
-    <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>29</v>
       </c>
@@ -6221,7 +6422,7 @@
       <c r="R64" s="9"/>
       <c r="S64" s="9"/>
     </row>
-    <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C65" s="5" t="s">
         <v>197</v>
       </c>
@@ -6275,7 +6476,7 @@
       <c r="R65" s="9"/>
       <c r="S65" s="9"/>
     </row>
-    <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C66" s="5" t="s">
         <v>197</v>
       </c>
@@ -6329,7 +6530,7 @@
       <c r="R66" s="9"/>
       <c r="S66" s="9"/>
     </row>
-    <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C67" s="5" t="s">
         <v>197</v>
       </c>
@@ -6381,12 +6582,12 @@
         <v>207</v>
       </c>
       <c r="R67" s="23" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="S67" s="9"/>
       <c r="U67" s="24"/>
     </row>
-    <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>35</v>
       </c>
@@ -6446,7 +6647,7 @@
       <c r="R68" s="9"/>
       <c r="S68" s="9"/>
     </row>
-    <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C69" s="12" t="s">
         <v>208</v>
       </c>
@@ -6500,7 +6701,7 @@
       <c r="R69" s="9"/>
       <c r="S69" s="9"/>
     </row>
-    <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>40</v>
       </c>
@@ -6562,7 +6763,7 @@
       </c>
       <c r="S70" s="9"/>
     </row>
-    <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C71" s="5" t="s">
         <v>219</v>
       </c>
@@ -6621,7 +6822,7 @@
       </c>
       <c r="U71" s="24"/>
     </row>
-    <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C72" s="5" t="s">
         <v>219</v>
       </c>
@@ -6670,7 +6871,7 @@
         <v>5</v>
       </c>
       <c r="Q72" s="23" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="R72" s="9" t="s">
         <v>172</v>
@@ -6679,11 +6880,11 @@
         <v>214</v>
       </c>
       <c r="T72" s="24" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="U72" s="24"/>
     </row>
-    <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>40</v>
       </c>
@@ -6746,7 +6947,7 @@
       <c r="S73" s="9"/>
       <c r="U73" s="24"/>
     </row>
-    <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C74" s="12" t="s">
         <v>225</v>
       </c>
@@ -6802,7 +7003,7 @@
       </c>
       <c r="S74" s="9"/>
     </row>
-    <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C75" s="12" t="s">
         <v>225</v>
       </c>
@@ -6854,12 +7055,12 @@
         <v>204</v>
       </c>
       <c r="R75" s="23" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="S75" s="9"/>
       <c r="U75" s="24"/>
     </row>
-    <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C76" s="12" t="s">
         <v>225</v>
       </c>
@@ -6911,12 +7112,12 @@
         <v>311</v>
       </c>
       <c r="R76" s="23" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="S76" s="9"/>
       <c r="U76" s="24"/>
     </row>
-    <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
         <v>50</v>
       </c>
@@ -6927,7 +7128,7 @@
         <v>228</v>
       </c>
       <c r="D77" s="29" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>230</v>
@@ -6977,7 +7178,7 @@
       <c r="S77" s="9"/>
       <c r="U77" s="24"/>
     </row>
-    <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C78" s="5" t="s">
         <v>228</v>
       </c>
@@ -7033,7 +7234,7 @@
       </c>
       <c r="S78" s="9"/>
     </row>
-    <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C79" s="5" t="s">
         <v>228</v>
       </c>
@@ -7088,7 +7289,7 @@
       <c r="S79" s="9"/>
       <c r="U79" s="24"/>
     </row>
-    <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C80" s="5" t="s">
         <v>228</v>
       </c>
@@ -7137,13 +7338,13 @@
         <v>10</v>
       </c>
       <c r="Q80" s="23" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="R80" s="9"/>
       <c r="S80" s="9"/>
       <c r="U80" s="24"/>
     </row>
-    <row r="81" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C81" s="5" t="s">
         <v>228</v>
       </c>
@@ -7200,7 +7401,7 @@
       <c r="S81" s="9"/>
       <c r="U81" s="24"/>
     </row>
-    <row r="82" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>60</v>
       </c>
@@ -7211,10 +7412,10 @@
         <v>322</v>
       </c>
       <c r="D82" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="E82" s="12" t="s">
         <v>333</v>
-      </c>
-      <c r="E82" s="12" t="s">
-        <v>334</v>
       </c>
       <c r="F82" s="12" t="s">
         <v>291</v>
@@ -7262,15 +7463,15 @@
       </c>
       <c r="S82" s="9"/>
     </row>
-    <row r="83" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C83" s="12" t="s">
         <v>322</v>
       </c>
       <c r="D83" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="E83" s="12" t="s">
         <v>335</v>
-      </c>
-      <c r="E83" s="12" t="s">
-        <v>336</v>
       </c>
       <c r="F83" s="12" t="s">
         <v>291</v>
@@ -7318,15 +7519,15 @@
       </c>
       <c r="S83" s="9"/>
     </row>
-    <row r="84" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C84" s="12" t="s">
         <v>322</v>
       </c>
       <c r="D84" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="E84" s="12" t="s">
         <v>337</v>
-      </c>
-      <c r="E84" s="12" t="s">
-        <v>338</v>
       </c>
       <c r="F84" s="12" t="s">
         <v>291</v>
@@ -7374,12 +7575,12 @@
       </c>
       <c r="S84" s="9"/>
     </row>
-    <row r="85" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C85" s="12" t="s">
         <v>294</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E85" s="12" t="s">
         <v>295</v>
@@ -7423,7 +7624,7 @@
         <v>8</v>
       </c>
       <c r="Q85" s="23" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="R85" s="23" t="s">
         <v>301</v>
@@ -7431,15 +7632,15 @@
       <c r="S85" s="9"/>
       <c r="U85" s="24"/>
     </row>
-    <row r="86" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C86" s="12" t="s">
         <v>294</v>
       </c>
       <c r="D86" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="E86" s="12" t="s">
         <v>340</v>
-      </c>
-      <c r="E86" s="12" t="s">
-        <v>341</v>
       </c>
       <c r="F86" s="12" t="s">
         <v>291</v>
@@ -7480,23 +7681,23 @@
         <v>6</v>
       </c>
       <c r="Q86" s="23" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R86" s="23" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="S86" s="9"/>
       <c r="U86" s="24"/>
     </row>
-    <row r="87" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C87" s="12" t="s">
         <v>294</v>
       </c>
       <c r="D87" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="E87" s="12" t="s">
         <v>342</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>343</v>
       </c>
       <c r="F87" s="12" t="s">
         <v>291</v>
@@ -7547,7 +7748,7 @@
       </c>
       <c r="U87" s="24"/>
     </row>
-    <row r="88" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C88" s="12" t="s">
         <v>322</v>
       </c>
@@ -7602,7 +7803,7 @@
       <c r="S88" s="23"/>
       <c r="U88" s="24"/>
     </row>
-    <row r="89" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
         <v>70</v>
       </c>
@@ -7666,11 +7867,11 @@
         <v>214</v>
       </c>
       <c r="T89" s="24" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="U89" s="24"/>
     </row>
-    <row r="90" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C90" s="5" t="s">
         <v>234</v>
       </c>
@@ -7729,7 +7930,7 @@
       </c>
       <c r="U90" s="24"/>
     </row>
-    <row r="91" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C91" s="5" t="s">
         <v>296</v>
       </c>
@@ -7786,7 +7987,7 @@
       <c r="S91" s="23"/>
       <c r="U91" s="24"/>
     </row>
-    <row r="92" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
         <v>80</v>
       </c>
@@ -7800,7 +8001,7 @@
         <v>240</v>
       </c>
       <c r="E92" s="26" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F92" s="12" t="s">
         <v>53</v>
@@ -7844,15 +8045,15 @@
         <v>241</v>
       </c>
       <c r="R92" s="23" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="S92" s="23" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="U92" s="24"/>
       <c r="W92" s="24"/>
     </row>
-    <row r="93" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C93" s="12" t="s">
         <v>324</v>
       </c>
@@ -7901,17 +8102,17 @@
         <v>6</v>
       </c>
       <c r="Q93" s="23" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="R93" s="23" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="S93" s="23" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U93" s="24"/>
     </row>
-    <row r="94" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C94" s="12" t="s">
         <v>239</v>
       </c>
@@ -7963,14 +8164,14 @@
         <v>283</v>
       </c>
       <c r="R94" s="23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="S94" s="23" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="U94" s="24"/>
     </row>
-    <row r="95" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
         <v>60</v>
       </c>
@@ -8011,11 +8212,11 @@
         <v>60</v>
       </c>
       <c r="M95" s="11">
-        <f t="shared" ref="M95:M119" si="51">I95*$M$2</f>
+        <f t="shared" ref="M95:M127" si="51">I95*$M$2</f>
         <v>62.5</v>
       </c>
       <c r="N95" s="11">
-        <f t="shared" ref="N95:N119" si="52">I95*$M$3</f>
+        <f t="shared" ref="N95:N127" si="52">I95*$M$3</f>
         <v>15</v>
       </c>
       <c r="O95" s="9">
@@ -8028,14 +8229,14 @@
         <v>284</v>
       </c>
       <c r="R95" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="S95" s="23" t="s">
         <v>354</v>
       </c>
-      <c r="S95" s="23" t="s">
-        <v>355</v>
-      </c>
       <c r="U95" s="24"/>
     </row>
-    <row r="96" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>75</v>
       </c>
@@ -8093,17 +8294,17 @@
         <v>252</v>
       </c>
       <c r="R96" s="23" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="S96" s="9" t="s">
         <v>253</v>
       </c>
       <c r="T96" s="24" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="U96" s="24"/>
     </row>
-    <row r="97" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C97" s="12" t="s">
         <v>249</v>
       </c>
@@ -8155,28 +8356,28 @@
         <v>146</v>
       </c>
       <c r="R97" s="23" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="S97" s="23" t="s">
         <v>285</v>
       </c>
       <c r="U97" s="24"/>
     </row>
-    <row r="98" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="B98" s="24" t="s">
         <v>384</v>
       </c>
-      <c r="B98" s="24" t="s">
+      <c r="C98" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="E98" s="5" t="s">
         <v>385</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>386</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>291</v>
@@ -8217,18 +8418,18 @@
         <v>6</v>
       </c>
       <c r="Q98" s="23" t="s">
+        <v>381</v>
+      </c>
+      <c r="R98" s="23" t="s">
         <v>382</v>
-      </c>
-      <c r="R98" s="23" t="s">
-        <v>383</v>
       </c>
       <c r="S98" s="23"/>
       <c r="T98" s="23" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="W98" s="24"/>
     </row>
-    <row r="99" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>105</v>
       </c>
@@ -8236,13 +8437,13 @@
         <v>125</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F99" s="12" t="s">
         <v>310</v>
@@ -8283,26 +8484,26 @@
         <v>8</v>
       </c>
       <c r="Q99" s="23" t="s">
+        <v>387</v>
+      </c>
+      <c r="R99" s="23" t="s">
         <v>388</v>
-      </c>
-      <c r="R99" s="23" t="s">
-        <v>389</v>
       </c>
       <c r="S99" s="23"/>
       <c r="T99" s="23" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="W99" s="24"/>
     </row>
-    <row r="100" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C100" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F100" s="12" t="s">
         <v>291</v>
@@ -8343,26 +8544,26 @@
         <v>9</v>
       </c>
       <c r="Q100" s="23" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="R100" s="23" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="S100" s="23"/>
       <c r="T100" s="23" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="W100" s="24"/>
     </row>
-    <row r="101" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C101" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F101" s="12" t="s">
         <v>291</v>
@@ -8403,7 +8604,7 @@
         <v>7</v>
       </c>
       <c r="Q101" s="23" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="R101" s="23" t="s">
         <v>316</v>
@@ -8412,15 +8613,15 @@
       <c r="T101" s="23"/>
       <c r="W101" s="24"/>
     </row>
-    <row r="102" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C102" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F102" s="12" t="s">
         <v>310</v>
@@ -8461,18 +8662,18 @@
         <v>7</v>
       </c>
       <c r="Q102" s="23" t="s">
+        <v>413</v>
+      </c>
+      <c r="R102" s="23" t="s">
         <v>414</v>
       </c>
-      <c r="R102" s="23" t="s">
-        <v>415</v>
-      </c>
       <c r="S102" s="23" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="T102" s="23"/>
       <c r="W102" s="24"/>
     </row>
-    <row r="103" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>120</v>
       </c>
@@ -8480,13 +8681,13 @@
         <v>140</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F103" s="5" t="s">
         <v>291</v>
@@ -8527,26 +8728,26 @@
         <v>9</v>
       </c>
       <c r="Q103" s="23" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="R103" s="23" t="s">
         <v>284</v>
       </c>
       <c r="S103" s="23"/>
       <c r="T103" s="23" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="W103" s="24"/>
     </row>
-    <row r="104" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C104" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F104" s="5" t="s">
         <v>310</v>
@@ -8587,18 +8788,18 @@
         <v>10</v>
       </c>
       <c r="Q104" s="23" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="R104" s="23" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="S104" s="23" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="T104" s="24"/>
       <c r="W104" s="24"/>
     </row>
-    <row r="105" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
         <v>135</v>
       </c>
@@ -8606,13 +8807,13 @@
         <v>155</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F105" s="12" t="s">
         <v>291</v>
@@ -8627,7 +8828,7 @@
         <v>24</v>
       </c>
       <c r="J105" s="17">
-        <f t="shared" ref="J105:J127" si="63">(G105*$I$2)+(H105*$I$3)</f>
+        <f t="shared" ref="J105:J135" si="63">(G105*$I$2)+(H105*$I$3)</f>
         <v>90</v>
       </c>
       <c r="K105" s="9">
@@ -8635,7 +8836,7 @@
         <v>31.5</v>
       </c>
       <c r="L105" s="10">
-        <f t="shared" ref="L105:L127" si="64">J105+K105</f>
+        <f t="shared" ref="L105:L135" si="64">J105+K105</f>
         <v>121.5</v>
       </c>
       <c r="M105" s="11">
@@ -8656,14 +8857,14 @@
         <v>241</v>
       </c>
       <c r="R105" s="24" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="S105" s="23" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="W105" s="24"/>
     </row>
-    <row r="106" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>165</v>
       </c>
@@ -8671,13 +8872,13 @@
         <v>180</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F106" s="5" t="s">
         <v>291</v>
@@ -8696,7 +8897,7 @@
         <v>121.5</v>
       </c>
       <c r="K106" s="9">
-        <f t="shared" ref="K106:K140" si="65">(G106*$I$4)+(H106*$I$5)+(I106*$I$7)</f>
+        <f t="shared" ref="K106:K147" si="65">(G106*$I$4)+(H106*$I$5)+(I106*$I$7)</f>
         <v>43.5</v>
       </c>
       <c r="L106" s="10">
@@ -8718,30 +8919,30 @@
         <v>16</v>
       </c>
       <c r="Q106" s="23" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="R106" s="23" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="S106" s="9" t="s">
         <v>241</v>
       </c>
       <c r="T106" s="24" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="W106" s="24" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="107" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C107" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>310</v>
@@ -8782,26 +8983,26 @@
         <v>8</v>
       </c>
       <c r="Q107" s="23" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R107" s="23" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="S107" s="23" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="T107" s="24"/>
       <c r="W107" s="24"/>
     </row>
-    <row r="108" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C108" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>291</v>
@@ -8842,26 +9043,26 @@
         <v>13</v>
       </c>
       <c r="Q108" s="23" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R108" s="24" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="S108" s="23" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="T108" s="24" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="U108" s="24" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="V108" s="24" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="W108" s="24"/>
     </row>
-    <row r="109" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
         <v>180</v>
       </c>
@@ -8869,13 +9070,13 @@
         <v>190</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F109" s="12" t="s">
         <v>291</v>
@@ -8919,14 +9120,14 @@
         <v>274</v>
       </c>
       <c r="R109" s="23" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="S109" s="23" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="W109" s="24"/>
     </row>
-    <row r="110" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>190</v>
       </c>
@@ -8934,13 +9135,13 @@
         <v>190</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F110" s="5" t="s">
         <v>291</v>
@@ -8981,17 +9182,17 @@
         <v>12</v>
       </c>
       <c r="Q110" s="23" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="R110" s="23" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="S110" s="23" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="W110" s="24"/>
     </row>
-    <row r="111" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
         <v>210</v>
       </c>
@@ -8999,13 +9200,13 @@
         <v>205</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F111" s="12" t="s">
         <v>291</v>
@@ -9046,535 +9247,626 @@
         <v>14</v>
       </c>
       <c r="Q111" s="23" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="R111" s="23" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="S111" s="23" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="W111" s="24"/>
     </row>
-    <row r="112" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="3">
-        <v>230</v>
-      </c>
-      <c r="B112" s="3">
+    <row r="112" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C112" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="D112" s="12"/>
+      <c r="E112" s="26" t="s">
+        <v>499</v>
+      </c>
+      <c r="F112" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="G112" s="12">
+        <v>64</v>
+      </c>
+      <c r="H112" s="12">
+        <v>50</v>
+      </c>
+      <c r="I112" s="12">
+        <v>34</v>
+      </c>
+      <c r="J112" s="17">
+        <f t="shared" ref="J112:J122" si="71">(G112*$I$2)+(H112*$I$3)</f>
+        <v>153</v>
+      </c>
+      <c r="K112" s="9">
+        <f t="shared" ref="K112:K122" si="72">(G112*$I$4)+(H112*$I$5)+(I112*$I$7)</f>
+        <v>57</v>
+      </c>
+      <c r="L112" s="10">
+        <f t="shared" ref="L112:L122" si="73">J112+K112</f>
         <v>210</v>
       </c>
-      <c r="C112" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="F112" s="5" t="s">
+      <c r="M112" s="11">
+        <f t="shared" ref="M112:M122" si="74">I112*$M$2</f>
+        <v>212.5</v>
+      </c>
+      <c r="N112" s="11">
+        <f t="shared" ref="N112:N122" si="75">I112*$M$3</f>
+        <v>51</v>
+      </c>
+      <c r="O112" s="9"/>
+      <c r="P112" s="9"/>
+      <c r="Q112" s="23"/>
+      <c r="R112" s="23"/>
+      <c r="S112" s="23"/>
+      <c r="W112" s="24"/>
+    </row>
+    <row r="113" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C113" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="D113" s="12"/>
+      <c r="E113" s="26" t="s">
+        <v>500</v>
+      </c>
+      <c r="F113" s="26" t="s">
         <v>291</v>
       </c>
-      <c r="G112" s="5">
+      <c r="G113" s="12">
+        <v>62</v>
+      </c>
+      <c r="H113" s="12">
+        <v>55</v>
+      </c>
+      <c r="I113" s="12">
+        <v>34</v>
+      </c>
+      <c r="J113" s="17">
+        <f t="shared" si="71"/>
+        <v>151.5</v>
+      </c>
+      <c r="K113" s="9">
+        <f t="shared" si="72"/>
+        <v>58.5</v>
+      </c>
+      <c r="L113" s="10">
+        <f t="shared" si="73"/>
+        <v>210</v>
+      </c>
+      <c r="M113" s="11">
+        <f t="shared" si="74"/>
+        <v>212.5</v>
+      </c>
+      <c r="N113" s="11">
+        <f t="shared" si="75"/>
+        <v>51</v>
+      </c>
+      <c r="O113" s="9"/>
+      <c r="P113" s="9"/>
+      <c r="Q113" s="23"/>
+      <c r="R113" s="23"/>
+      <c r="S113" s="23"/>
+      <c r="W113" s="24"/>
+    </row>
+    <row r="114" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C114" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="D114" s="12"/>
+      <c r="E114" s="26" t="s">
+        <v>501</v>
+      </c>
+      <c r="F114" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G114" s="12">
         <v>68</v>
       </c>
-      <c r="H112" s="5">
-        <v>60</v>
-      </c>
-      <c r="I112" s="5">
-        <v>32</v>
-      </c>
-      <c r="J112" s="17">
-        <f t="shared" si="63"/>
-        <v>166</v>
-      </c>
-      <c r="K112" s="9">
-        <f t="shared" si="65"/>
-        <v>64</v>
-      </c>
-      <c r="L112" s="10">
-        <f t="shared" si="64"/>
-        <v>230</v>
-      </c>
-      <c r="M112" s="11">
-        <f t="shared" si="51"/>
-        <v>200</v>
-      </c>
-      <c r="N112" s="11">
-        <f t="shared" si="52"/>
-        <v>48</v>
-      </c>
-      <c r="O112" s="9">
-        <v>8</v>
-      </c>
-      <c r="P112" s="9">
-        <v>14</v>
-      </c>
-      <c r="Q112" s="23" t="s">
-        <v>436</v>
-      </c>
-      <c r="R112" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="S112" s="23" t="s">
-        <v>444</v>
-      </c>
-      <c r="T112" s="23" t="s">
-        <v>437</v>
-      </c>
-      <c r="W112" s="24"/>
-    </row>
-    <row r="113" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C113" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="G113" s="5">
-        <v>74</v>
-      </c>
-      <c r="H113" s="5">
-        <v>45</v>
-      </c>
-      <c r="I113" s="5">
-        <v>34</v>
-      </c>
-      <c r="J113" s="17">
-        <f t="shared" ref="J113:J114" si="71">(G113*$I$2)+(H113*$I$3)</f>
-        <v>170.5</v>
-      </c>
-      <c r="K113" s="9">
-        <f t="shared" ref="K113:K114" si="72">(G113*$I$4)+(H113*$I$5)+(I113*$I$7)</f>
-        <v>59.5</v>
-      </c>
-      <c r="L113" s="10">
-        <f t="shared" ref="L113:L114" si="73">J113+K113</f>
-        <v>230</v>
-      </c>
-      <c r="M113" s="11">
-        <f t="shared" ref="M113:M114" si="74">I113*$M$2</f>
-        <v>212.5</v>
-      </c>
-      <c r="N113" s="11">
-        <f t="shared" ref="N113:N114" si="75">I113*$M$3</f>
-        <v>51</v>
-      </c>
-      <c r="O113" s="9">
-        <v>8</v>
-      </c>
-      <c r="P113" s="9">
-        <v>12</v>
-      </c>
-      <c r="Q113" s="23" t="s">
-        <v>420</v>
-      </c>
-      <c r="R113" s="23" t="s">
-        <v>440</v>
-      </c>
-      <c r="S113" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="T113" s="24" t="s">
-        <v>441</v>
-      </c>
-      <c r="W113" s="24"/>
-    </row>
-    <row r="114" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C114" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="G114" s="5">
-        <v>64</v>
-      </c>
-      <c r="H114" s="5">
-        <v>72</v>
-      </c>
-      <c r="I114" s="5">
-        <v>34</v>
+      <c r="H114" s="12">
+        <v>40</v>
+      </c>
+      <c r="I114" s="12">
+        <v>33</v>
       </c>
       <c r="J114" s="17">
         <f t="shared" si="71"/>
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="K114" s="9">
         <f t="shared" si="72"/>
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="L114" s="10">
         <f t="shared" si="73"/>
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="M114" s="11">
         <f t="shared" si="74"/>
-        <v>212.5</v>
+        <v>206.25</v>
       </c>
       <c r="N114" s="11">
         <f t="shared" si="75"/>
-        <v>51</v>
-      </c>
-      <c r="O114" s="9">
-        <v>10</v>
-      </c>
-      <c r="P114" s="9">
-        <v>16</v>
-      </c>
-      <c r="Q114" s="23" t="s">
-        <v>438</v>
-      </c>
-      <c r="R114" s="23" t="s">
-        <v>431</v>
-      </c>
-      <c r="S114" s="23" t="s">
-        <v>439</v>
-      </c>
+        <v>49.5</v>
+      </c>
+      <c r="O114" s="9"/>
+      <c r="P114" s="9"/>
+      <c r="Q114" s="23"/>
+      <c r="R114" s="23"/>
+      <c r="S114" s="23"/>
       <c r="W114" s="24"/>
     </row>
-    <row r="115" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="3">
-        <v>240</v>
-      </c>
-      <c r="B115" s="3">
-        <v>210</v>
-      </c>
+    <row r="115" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C115" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="D115" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="E115" s="12" t="s">
-        <v>428</v>
+        <v>373</v>
+      </c>
+      <c r="D115" s="12"/>
+      <c r="E115" s="26" t="s">
+        <v>502</v>
       </c>
       <c r="F115" s="12" t="s">
         <v>291</v>
       </c>
       <c r="G115" s="12">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="H115" s="12">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I115" s="12">
+        <v>33</v>
+      </c>
+      <c r="J115" s="17">
+        <f t="shared" si="71"/>
+        <v>148.5</v>
+      </c>
+      <c r="K115" s="9">
+        <f t="shared" si="72"/>
+        <v>61.5</v>
+      </c>
+      <c r="L115" s="10">
+        <f t="shared" si="73"/>
+        <v>210</v>
+      </c>
+      <c r="M115" s="11">
+        <f t="shared" si="74"/>
+        <v>206.25</v>
+      </c>
+      <c r="N115" s="11">
+        <f t="shared" si="75"/>
+        <v>49.5</v>
+      </c>
+      <c r="O115" s="9"/>
+      <c r="P115" s="9"/>
+      <c r="Q115" s="23"/>
+      <c r="R115" s="23"/>
+      <c r="S115" s="23"/>
+      <c r="W115" s="24"/>
+    </row>
+    <row r="116" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="3">
+        <v>230</v>
+      </c>
+      <c r="B116" s="3">
+        <v>210</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G116" s="5">
+        <v>68</v>
+      </c>
+      <c r="H116" s="5">
+        <v>60</v>
+      </c>
+      <c r="I116" s="5">
+        <v>32</v>
+      </c>
+      <c r="J116" s="17">
+        <f t="shared" si="71"/>
+        <v>166</v>
+      </c>
+      <c r="K116" s="9">
+        <f t="shared" si="72"/>
+        <v>64</v>
+      </c>
+      <c r="L116" s="10">
+        <f t="shared" si="73"/>
+        <v>230</v>
+      </c>
+      <c r="M116" s="11">
+        <f t="shared" si="74"/>
+        <v>200</v>
+      </c>
+      <c r="N116" s="11">
+        <f t="shared" si="75"/>
+        <v>48</v>
+      </c>
+      <c r="O116" s="9">
+        <v>8</v>
+      </c>
+      <c r="P116" s="9">
+        <v>14</v>
+      </c>
+      <c r="Q116" s="23" t="s">
+        <v>434</v>
+      </c>
+      <c r="R116" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="S116" s="23" t="s">
+        <v>442</v>
+      </c>
+      <c r="T116" s="23" t="s">
+        <v>435</v>
+      </c>
+      <c r="W116" s="24"/>
+    </row>
+    <row r="117" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C117" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G117" s="5">
+        <v>74</v>
+      </c>
+      <c r="H117" s="5">
+        <v>45</v>
+      </c>
+      <c r="I117" s="5">
         <v>34</v>
       </c>
-      <c r="J115" s="17">
-        <f t="shared" si="63"/>
-        <v>174.5</v>
-      </c>
-      <c r="K115" s="9">
-        <f t="shared" si="65"/>
-        <v>65</v>
-      </c>
-      <c r="L115" s="10">
-        <f t="shared" si="64"/>
-        <v>239.5</v>
-      </c>
-      <c r="M115" s="11">
-        <f t="shared" si="51"/>
+      <c r="J117" s="17">
+        <f t="shared" si="71"/>
+        <v>170.5</v>
+      </c>
+      <c r="K117" s="9">
+        <f t="shared" si="72"/>
+        <v>59.5</v>
+      </c>
+      <c r="L117" s="10">
+        <f t="shared" si="73"/>
+        <v>230</v>
+      </c>
+      <c r="M117" s="11">
+        <f t="shared" si="74"/>
         <v>212.5</v>
       </c>
-      <c r="N115" s="11">
-        <f t="shared" si="52"/>
+      <c r="N117" s="11">
+        <f t="shared" si="75"/>
         <v>51</v>
       </c>
-      <c r="O115" s="9">
+      <c r="O117" s="9">
         <v>8</v>
       </c>
-      <c r="P115" s="9">
+      <c r="P117" s="9">
+        <v>12</v>
+      </c>
+      <c r="Q117" s="23" t="s">
+        <v>419</v>
+      </c>
+      <c r="R117" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="S117" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="T117" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="W117" s="24"/>
+    </row>
+    <row r="118" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C118" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G118" s="5">
+        <v>64</v>
+      </c>
+      <c r="H118" s="5">
+        <v>72</v>
+      </c>
+      <c r="I118" s="5">
+        <v>34</v>
+      </c>
+      <c r="J118" s="17">
+        <f t="shared" si="71"/>
+        <v>164</v>
+      </c>
+      <c r="K118" s="9">
+        <f t="shared" si="72"/>
+        <v>68</v>
+      </c>
+      <c r="L118" s="10">
+        <f t="shared" si="73"/>
+        <v>232</v>
+      </c>
+      <c r="M118" s="11">
+        <f t="shared" si="74"/>
+        <v>212.5</v>
+      </c>
+      <c r="N118" s="11">
+        <f t="shared" si="75"/>
+        <v>51</v>
+      </c>
+      <c r="O118" s="9">
+        <v>10</v>
+      </c>
+      <c r="P118" s="9">
         <v>16</v>
       </c>
-      <c r="Q115" s="23" t="s">
-        <v>443</v>
-      </c>
-      <c r="R115" s="23" t="s">
-        <v>442</v>
-      </c>
-      <c r="S115" s="23" t="s">
-        <v>435</v>
-      </c>
-      <c r="W115" s="24"/>
-    </row>
-    <row r="116" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C116" s="9"/>
-      <c r="D116" s="9"/>
-      <c r="E116" s="9"/>
-      <c r="F116" s="9"/>
-      <c r="G116" s="9"/>
-      <c r="H116" s="9"/>
-      <c r="I116" s="9"/>
-      <c r="J116" s="17">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="K116" s="9">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="L116" s="10">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M116" s="11">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="N116" s="11">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="O116" s="9"/>
-      <c r="P116" s="9"/>
-      <c r="Q116" s="9"/>
-      <c r="R116" s="9"/>
-      <c r="S116" s="9"/>
-    </row>
-    <row r="117" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C117" s="9"/>
-      <c r="D117" s="9"/>
-      <c r="E117" s="9"/>
-      <c r="F117" s="9"/>
-      <c r="G117" s="9"/>
-      <c r="H117" s="9"/>
-      <c r="I117" s="9"/>
-      <c r="J117" s="17">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="K117" s="9">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="L117" s="10">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M117" s="11">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="N117" s="11">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="O117" s="9"/>
-      <c r="P117" s="9"/>
-      <c r="Q117" s="9"/>
-      <c r="R117" s="9"/>
-      <c r="S117" s="9"/>
-    </row>
-    <row r="118" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C118" s="9"/>
-      <c r="D118" s="9"/>
-      <c r="E118" s="9"/>
-      <c r="F118" s="9"/>
-      <c r="G118" s="9"/>
-      <c r="H118" s="9"/>
-      <c r="I118" s="9"/>
-      <c r="J118" s="17">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="K118" s="9">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="L118" s="10">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M118" s="11">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="N118" s="11">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="O118" s="9"/>
-      <c r="P118" s="9"/>
-      <c r="Q118" s="9"/>
-      <c r="R118" s="9"/>
-      <c r="S118" s="9"/>
-    </row>
-    <row r="119" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C119" s="9"/>
-      <c r="D119" s="9"/>
-      <c r="E119" s="9"/>
-      <c r="F119" s="9"/>
-      <c r="G119" s="9"/>
-      <c r="H119" s="9"/>
-      <c r="I119" s="9"/>
+      <c r="Q118" s="23" t="s">
+        <v>436</v>
+      </c>
+      <c r="R118" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="S118" s="23" t="s">
+        <v>437</v>
+      </c>
+      <c r="W118" s="24"/>
+    </row>
+    <row r="119" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C119" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="D119" s="5"/>
+      <c r="E119" s="25" t="s">
+        <v>503</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="G119" s="5">
+        <v>50</v>
+      </c>
+      <c r="H119" s="5">
+        <v>100</v>
+      </c>
+      <c r="I119" s="5">
+        <v>32</v>
+      </c>
       <c r="J119" s="17">
-        <f t="shared" si="63"/>
-        <v>0</v>
+        <f t="shared" si="71"/>
+        <v>150</v>
       </c>
       <c r="K119" s="9">
-        <f t="shared" si="65"/>
-        <v>0</v>
+        <f t="shared" si="72"/>
+        <v>75</v>
       </c>
       <c r="L119" s="10">
-        <f t="shared" si="64"/>
-        <v>0</v>
+        <f t="shared" si="73"/>
+        <v>225</v>
       </c>
       <c r="M119" s="11">
-        <f t="shared" si="51"/>
-        <v>0</v>
+        <f t="shared" si="74"/>
+        <v>200</v>
       </c>
       <c r="N119" s="11">
-        <f t="shared" si="52"/>
-        <v>0</v>
+        <f t="shared" si="75"/>
+        <v>48</v>
       </c>
       <c r="O119" s="9"/>
       <c r="P119" s="9"/>
-      <c r="Q119" s="9"/>
-      <c r="R119" s="9"/>
-      <c r="S119" s="9"/>
-    </row>
-    <row r="120" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C120" s="9"/>
-      <c r="D120" s="9"/>
-      <c r="E120" s="9"/>
-      <c r="F120" s="9"/>
-      <c r="G120" s="9"/>
-      <c r="H120" s="9"/>
-      <c r="I120" s="9"/>
+      <c r="Q119" s="23"/>
+      <c r="R119" s="23"/>
+      <c r="S119" s="23"/>
+      <c r="W119" s="24"/>
+    </row>
+    <row r="120" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C120" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="D120" s="5"/>
+      <c r="E120" s="25" t="s">
+        <v>504</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G120" s="5">
+        <v>60</v>
+      </c>
+      <c r="H120" s="5">
+        <v>80</v>
+      </c>
+      <c r="I120" s="5">
+        <v>33</v>
+      </c>
       <c r="J120" s="17">
-        <f t="shared" si="63"/>
-        <v>0</v>
+        <f t="shared" si="71"/>
+        <v>160</v>
       </c>
       <c r="K120" s="9">
-        <f t="shared" si="65"/>
-        <v>0</v>
+        <f t="shared" si="72"/>
+        <v>70</v>
       </c>
       <c r="L120" s="10">
-        <f t="shared" si="64"/>
-        <v>0</v>
+        <f t="shared" si="73"/>
+        <v>230</v>
       </c>
       <c r="M120" s="11">
-        <f t="shared" ref="M120:M163" si="76">I120*$M$2</f>
-        <v>0</v>
+        <f t="shared" si="74"/>
+        <v>206.25</v>
       </c>
       <c r="N120" s="11">
-        <f t="shared" ref="N120:N163" si="77">I120*$M$3</f>
-        <v>0</v>
+        <f t="shared" si="75"/>
+        <v>49.5</v>
       </c>
       <c r="O120" s="9"/>
       <c r="P120" s="9"/>
-      <c r="Q120" s="9"/>
-      <c r="R120" s="9"/>
-      <c r="S120" s="9"/>
-    </row>
-    <row r="121" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C121" s="9"/>
-      <c r="D121" s="9"/>
-      <c r="E121" s="9"/>
-      <c r="F121" s="9"/>
-      <c r="G121" s="9"/>
-      <c r="H121" s="9"/>
-      <c r="I121" s="9"/>
+      <c r="Q120" s="23"/>
+      <c r="R120" s="23"/>
+      <c r="S120" s="23"/>
+      <c r="W120" s="24"/>
+    </row>
+    <row r="121" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C121" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="D121" s="5"/>
+      <c r="E121" s="25" t="s">
+        <v>505</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G121" s="5">
+        <v>72</v>
+      </c>
+      <c r="H121" s="5">
+        <v>50</v>
+      </c>
+      <c r="I121" s="5">
+        <v>33</v>
+      </c>
       <c r="J121" s="17">
-        <f t="shared" si="63"/>
-        <v>0</v>
+        <f t="shared" si="71"/>
+        <v>169</v>
       </c>
       <c r="K121" s="9">
-        <f t="shared" si="65"/>
-        <v>0</v>
+        <f t="shared" si="72"/>
+        <v>61</v>
       </c>
       <c r="L121" s="10">
-        <f t="shared" si="64"/>
-        <v>0</v>
+        <f t="shared" si="73"/>
+        <v>230</v>
       </c>
       <c r="M121" s="11">
-        <f t="shared" si="76"/>
-        <v>0</v>
+        <f t="shared" si="74"/>
+        <v>206.25</v>
       </c>
       <c r="N121" s="11">
-        <f t="shared" si="77"/>
-        <v>0</v>
+        <f t="shared" si="75"/>
+        <v>49.5</v>
       </c>
       <c r="O121" s="9"/>
       <c r="P121" s="9"/>
-      <c r="Q121" s="9"/>
-      <c r="R121" s="9"/>
-      <c r="S121" s="9"/>
-    </row>
-    <row r="122" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C122" s="9"/>
-      <c r="D122" s="9"/>
-      <c r="E122" s="9"/>
-      <c r="F122" s="9"/>
-      <c r="G122" s="9"/>
-      <c r="H122" s="9"/>
-      <c r="I122" s="9"/>
+      <c r="Q121" s="23"/>
+      <c r="R121" s="23"/>
+      <c r="S121" s="23"/>
+      <c r="W121" s="24"/>
+    </row>
+    <row r="122" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="3">
+        <v>240</v>
+      </c>
+      <c r="B122" s="3">
+        <v>210</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="D122" s="26"/>
+      <c r="E122" s="26" t="s">
+        <v>506</v>
+      </c>
+      <c r="F122" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="G122" s="26">
+        <v>52</v>
+      </c>
+      <c r="H122" s="26">
+        <v>105</v>
+      </c>
+      <c r="I122" s="26">
+        <v>33</v>
+      </c>
       <c r="J122" s="17">
-        <f t="shared" si="63"/>
-        <v>0</v>
+        <f t="shared" si="71"/>
+        <v>156.5</v>
       </c>
       <c r="K122" s="9">
-        <f t="shared" si="65"/>
-        <v>0</v>
+        <f t="shared" si="72"/>
+        <v>78.5</v>
       </c>
       <c r="L122" s="10">
-        <f t="shared" si="64"/>
-        <v>0</v>
+        <f t="shared" si="73"/>
+        <v>235</v>
       </c>
       <c r="M122" s="11">
-        <f t="shared" si="76"/>
-        <v>0</v>
+        <f t="shared" si="74"/>
+        <v>206.25</v>
       </c>
       <c r="N122" s="11">
-        <f t="shared" si="77"/>
-        <v>0</v>
+        <f t="shared" si="75"/>
+        <v>49.5</v>
       </c>
       <c r="O122" s="9"/>
       <c r="P122" s="9"/>
-      <c r="Q122" s="9"/>
-      <c r="R122" s="9"/>
-      <c r="S122" s="9"/>
-    </row>
-    <row r="123" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C123" s="9"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="9"/>
-      <c r="F123" s="9"/>
-      <c r="G123" s="9"/>
-      <c r="H123" s="9"/>
-      <c r="I123" s="9"/>
+      <c r="Q122" s="23"/>
+      <c r="R122" s="23"/>
+      <c r="S122" s="23"/>
+      <c r="W122" s="24"/>
+    </row>
+    <row r="123" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C123" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="D123" s="26"/>
+      <c r="E123" s="26" t="s">
+        <v>507</v>
+      </c>
+      <c r="F123" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G123" s="26">
+        <v>82</v>
+      </c>
+      <c r="H123" s="26">
+        <v>30</v>
+      </c>
+      <c r="I123" s="26">
+        <v>33</v>
+      </c>
       <c r="J123" s="17">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="K123" s="9">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L123" s="10">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="M123" s="11">
-        <f t="shared" si="76"/>
-        <v>0</v>
+        <f t="shared" si="51"/>
+        <v>206.25</v>
       </c>
       <c r="N123" s="11">
-        <f t="shared" si="77"/>
-        <v>0</v>
+        <f t="shared" si="52"/>
+        <v>49.5</v>
       </c>
       <c r="O123" s="9"/>
       <c r="P123" s="9"/>
@@ -9582,67 +9874,109 @@
       <c r="R123" s="9"/>
       <c r="S123" s="9"/>
     </row>
-    <row r="124" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C124" s="9"/>
-      <c r="D124" s="9"/>
-      <c r="E124" s="9"/>
-      <c r="F124" s="9"/>
-      <c r="G124" s="9"/>
-      <c r="H124" s="9"/>
-      <c r="I124" s="9"/>
+    <row r="124" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C124" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="D124" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="E124" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="F124" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G124" s="12">
+        <v>73</v>
+      </c>
+      <c r="H124" s="12">
+        <v>57</v>
+      </c>
+      <c r="I124" s="12">
+        <v>35</v>
+      </c>
       <c r="J124" s="17">
-        <f t="shared" si="63"/>
-        <v>0</v>
+        <f>(G124*$I$2)+(H124*$I$3)</f>
+        <v>174.5</v>
       </c>
       <c r="K124" s="9">
-        <f t="shared" si="65"/>
-        <v>0</v>
+        <f>(G124*$I$4)+(H124*$I$5)+(I124*$I$7)</f>
+        <v>65</v>
       </c>
       <c r="L124" s="10">
-        <f t="shared" si="64"/>
-        <v>0</v>
+        <f>J124+K124</f>
+        <v>239.5</v>
       </c>
       <c r="M124" s="11">
-        <f t="shared" si="76"/>
-        <v>0</v>
+        <f>I124*$M$2</f>
+        <v>218.75</v>
       </c>
       <c r="N124" s="11">
-        <f t="shared" si="77"/>
-        <v>0</v>
-      </c>
-      <c r="O124" s="9"/>
-      <c r="P124" s="9"/>
-      <c r="Q124" s="9"/>
-      <c r="R124" s="9"/>
-      <c r="S124" s="9"/>
-    </row>
-    <row r="125" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C125" s="9"/>
-      <c r="D125" s="9"/>
-      <c r="E125" s="9"/>
-      <c r="F125" s="9"/>
-      <c r="G125" s="9"/>
-      <c r="H125" s="9"/>
-      <c r="I125" s="9"/>
+        <f>I124*$M$3</f>
+        <v>52.5</v>
+      </c>
+      <c r="O124" s="9">
+        <v>8</v>
+      </c>
+      <c r="P124" s="9">
+        <v>16</v>
+      </c>
+      <c r="Q124" s="23" t="s">
+        <v>441</v>
+      </c>
+      <c r="R124" s="23" t="s">
+        <v>440</v>
+      </c>
+      <c r="S124" s="23" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="3">
+        <v>240</v>
+      </c>
+      <c r="B125" s="3">
+        <v>210</v>
+      </c>
+      <c r="C125" s="25" t="s">
+        <v>517</v>
+      </c>
+      <c r="D125" s="25"/>
+      <c r="E125" s="25" t="s">
+        <v>508</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G125" s="25">
+        <v>84</v>
+      </c>
+      <c r="H125" s="25">
+        <v>30</v>
+      </c>
+      <c r="I125" s="25">
+        <v>33.5</v>
+      </c>
       <c r="J125" s="17">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="K125" s="9">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="L125" s="10">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="M125" s="11">
-        <f t="shared" si="76"/>
-        <v>0</v>
+        <f t="shared" si="51"/>
+        <v>209.375</v>
       </c>
       <c r="N125" s="11">
-        <f t="shared" si="77"/>
-        <v>0</v>
+        <f t="shared" si="52"/>
+        <v>50.25</v>
       </c>
       <c r="O125" s="9"/>
       <c r="P125" s="9"/>
@@ -9650,33 +9984,45 @@
       <c r="R125" s="9"/>
       <c r="S125" s="9"/>
     </row>
-    <row r="126" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C126" s="9"/>
-      <c r="D126" s="9"/>
-      <c r="E126" s="9"/>
-      <c r="F126" s="9"/>
-      <c r="G126" s="9"/>
-      <c r="H126" s="9"/>
-      <c r="I126" s="9"/>
+    <row r="126" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C126" s="25" t="s">
+        <v>517</v>
+      </c>
+      <c r="D126" s="25"/>
+      <c r="E126" s="25" t="s">
+        <v>509</v>
+      </c>
+      <c r="F126" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G126" s="25">
+        <v>68</v>
+      </c>
+      <c r="H126" s="25">
+        <v>70</v>
+      </c>
+      <c r="I126" s="25">
+        <v>33</v>
+      </c>
       <c r="J126" s="17">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="K126" s="9">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="L126" s="10">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="M126" s="11">
-        <f t="shared" si="76"/>
-        <v>0</v>
+        <f t="shared" si="51"/>
+        <v>206.25</v>
       </c>
       <c r="N126" s="11">
-        <f t="shared" si="77"/>
-        <v>0</v>
+        <f t="shared" si="52"/>
+        <v>49.5</v>
       </c>
       <c r="O126" s="9"/>
       <c r="P126" s="9"/>
@@ -9684,33 +10030,45 @@
       <c r="R126" s="9"/>
       <c r="S126" s="9"/>
     </row>
-    <row r="127" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C127" s="9"/>
-      <c r="D127" s="9"/>
-      <c r="E127" s="9"/>
-      <c r="F127" s="9"/>
-      <c r="G127" s="9"/>
-      <c r="H127" s="9"/>
-      <c r="I127" s="9"/>
+    <row r="127" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C127" s="25" t="s">
+        <v>517</v>
+      </c>
+      <c r="D127" s="25"/>
+      <c r="E127" s="25" t="s">
+        <v>510</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G127" s="25">
+        <v>70</v>
+      </c>
+      <c r="H127" s="25">
+        <v>64</v>
+      </c>
+      <c r="I127" s="25">
+        <v>32</v>
+      </c>
       <c r="J127" s="17">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="K127" s="9">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L127" s="10">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="M127" s="11">
-        <f t="shared" si="76"/>
-        <v>0</v>
+        <f t="shared" si="51"/>
+        <v>200</v>
       </c>
       <c r="N127" s="11">
-        <f t="shared" si="77"/>
-        <v>0</v>
+        <f t="shared" si="52"/>
+        <v>48</v>
       </c>
       <c r="O127" s="9"/>
       <c r="P127" s="9"/>
@@ -9718,33 +10076,51 @@
       <c r="R127" s="9"/>
       <c r="S127" s="9"/>
     </row>
-    <row r="128" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C128" s="9"/>
-      <c r="D128" s="9"/>
-      <c r="E128" s="9"/>
-      <c r="F128" s="9"/>
-      <c r="G128" s="9"/>
-      <c r="H128" s="9"/>
-      <c r="I128" s="9"/>
+    <row r="128" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="3">
+        <v>240</v>
+      </c>
+      <c r="B128" s="3">
+        <v>210</v>
+      </c>
+      <c r="C128" s="26" t="s">
+        <v>518</v>
+      </c>
+      <c r="D128" s="12"/>
+      <c r="E128" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="F128" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G128" s="12">
+        <v>71</v>
+      </c>
+      <c r="H128" s="12">
+        <v>63</v>
+      </c>
+      <c r="I128" s="12">
+        <v>33</v>
+      </c>
       <c r="J128" s="17">
-        <f t="shared" ref="J128:J163" si="78">(G128*$I$2)+(H128*$I$3)</f>
-        <v>0</v>
+        <f t="shared" si="63"/>
+        <v>173.5</v>
       </c>
       <c r="K128" s="9">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L128" s="10">
-        <f t="shared" ref="L128:L163" si="79">J128+K128</f>
-        <v>0</v>
+        <f t="shared" si="64"/>
+        <v>240.5</v>
       </c>
       <c r="M128" s="11">
-        <f t="shared" si="76"/>
-        <v>0</v>
+        <f t="shared" ref="M128:M170" si="76">I128*$M$2</f>
+        <v>206.25</v>
       </c>
       <c r="N128" s="11">
-        <f t="shared" si="77"/>
-        <v>0</v>
+        <f t="shared" ref="N128:N170" si="77">I128*$M$3</f>
+        <v>49.5</v>
       </c>
       <c r="O128" s="9"/>
       <c r="P128" s="9"/>
@@ -9752,33 +10128,45 @@
       <c r="R128" s="9"/>
       <c r="S128" s="9"/>
     </row>
-    <row r="129" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C129" s="9"/>
-      <c r="D129" s="9"/>
-      <c r="E129" s="9"/>
-      <c r="F129" s="9"/>
-      <c r="G129" s="9"/>
-      <c r="H129" s="9"/>
-      <c r="I129" s="9"/>
+    <row r="129" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C129" s="26" t="s">
+        <v>518</v>
+      </c>
+      <c r="D129" s="12"/>
+      <c r="E129" s="12" t="s">
+        <v>512</v>
+      </c>
+      <c r="F129" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G129" s="12">
+        <v>68</v>
+      </c>
+      <c r="H129" s="12">
+        <v>70</v>
+      </c>
+      <c r="I129" s="12">
+        <v>33</v>
+      </c>
       <c r="J129" s="17">
-        <f t="shared" si="78"/>
-        <v>0</v>
+        <f t="shared" si="63"/>
+        <v>171</v>
       </c>
       <c r="K129" s="9">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="L129" s="10">
-        <f t="shared" si="79"/>
-        <v>0</v>
+        <f t="shared" si="64"/>
+        <v>240</v>
       </c>
       <c r="M129" s="11">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>206.25</v>
       </c>
       <c r="N129" s="11">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>49.5</v>
       </c>
       <c r="O129" s="9"/>
       <c r="P129" s="9"/>
@@ -9786,33 +10174,51 @@
       <c r="R129" s="9"/>
       <c r="S129" s="9"/>
     </row>
-    <row r="130" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C130" s="9"/>
-      <c r="D130" s="9"/>
-      <c r="E130" s="9"/>
-      <c r="F130" s="9"/>
-      <c r="G130" s="9"/>
-      <c r="H130" s="9"/>
-      <c r="I130" s="9"/>
+    <row r="130" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="3">
+        <v>240</v>
+      </c>
+      <c r="B130" s="3">
+        <v>210</v>
+      </c>
+      <c r="C130" s="25" t="s">
+        <v>519</v>
+      </c>
+      <c r="D130" s="25"/>
+      <c r="E130" s="25" t="s">
+        <v>513</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G130" s="25">
+        <v>50</v>
+      </c>
+      <c r="H130" s="25">
+        <v>115</v>
+      </c>
+      <c r="I130" s="25">
+        <v>33</v>
+      </c>
       <c r="J130" s="17">
-        <f t="shared" si="78"/>
-        <v>0</v>
+        <f t="shared" si="63"/>
+        <v>157.5</v>
       </c>
       <c r="K130" s="9">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="L130" s="10">
-        <f t="shared" si="79"/>
-        <v>0</v>
+        <f t="shared" si="64"/>
+        <v>240</v>
       </c>
       <c r="M130" s="11">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>206.25</v>
       </c>
       <c r="N130" s="11">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>49.5</v>
       </c>
       <c r="O130" s="9"/>
       <c r="P130" s="9"/>
@@ -9820,33 +10226,45 @@
       <c r="R130" s="9"/>
       <c r="S130" s="9"/>
     </row>
-    <row r="131" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C131" s="9"/>
-      <c r="D131" s="9"/>
-      <c r="E131" s="9"/>
-      <c r="F131" s="9"/>
-      <c r="G131" s="9"/>
-      <c r="H131" s="9"/>
-      <c r="I131" s="9"/>
+    <row r="131" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C131" s="25" t="s">
+        <v>519</v>
+      </c>
+      <c r="D131" s="25"/>
+      <c r="E131" s="25" t="s">
+        <v>514</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G131" s="25">
+        <v>65</v>
+      </c>
+      <c r="H131" s="25">
+        <v>77</v>
+      </c>
+      <c r="I131" s="25">
+        <v>33</v>
+      </c>
       <c r="J131" s="17">
-        <f t="shared" si="78"/>
-        <v>0</v>
+        <f t="shared" si="63"/>
+        <v>168.5</v>
       </c>
       <c r="K131" s="9">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="L131" s="10">
-        <f t="shared" si="79"/>
-        <v>0</v>
+        <f t="shared" si="64"/>
+        <v>239.5</v>
       </c>
       <c r="M131" s="11">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>206.25</v>
       </c>
       <c r="N131" s="11">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>49.5</v>
       </c>
       <c r="O131" s="9"/>
       <c r="P131" s="9"/>
@@ -9854,33 +10272,51 @@
       <c r="R131" s="9"/>
       <c r="S131" s="9"/>
     </row>
-    <row r="132" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C132" s="9"/>
-      <c r="D132" s="9"/>
-      <c r="E132" s="9"/>
-      <c r="F132" s="9"/>
-      <c r="G132" s="9"/>
-      <c r="H132" s="9"/>
-      <c r="I132" s="9"/>
+    <row r="132" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="3">
+        <v>245</v>
+      </c>
+      <c r="B132" s="3">
+        <v>215</v>
+      </c>
+      <c r="C132" s="26" t="s">
+        <v>520</v>
+      </c>
+      <c r="D132" s="12"/>
+      <c r="E132" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="F132" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G132" s="12">
+        <v>72</v>
+      </c>
+      <c r="H132" s="12">
+        <v>65</v>
+      </c>
+      <c r="I132" s="12">
+        <v>34.5</v>
+      </c>
       <c r="J132" s="17">
-        <f t="shared" si="78"/>
-        <v>0</v>
+        <f t="shared" si="63"/>
+        <v>176.5</v>
       </c>
       <c r="K132" s="9">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>68.5</v>
       </c>
       <c r="L132" s="10">
-        <f t="shared" si="79"/>
-        <v>0</v>
+        <f t="shared" si="64"/>
+        <v>245</v>
       </c>
       <c r="M132" s="11">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>215.625</v>
       </c>
       <c r="N132" s="11">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>51.75</v>
       </c>
       <c r="O132" s="9"/>
       <c r="P132" s="9"/>
@@ -9888,33 +10324,51 @@
       <c r="R132" s="9"/>
       <c r="S132" s="9"/>
     </row>
-    <row r="133" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C133" s="9"/>
-      <c r="D133" s="9"/>
-      <c r="E133" s="9"/>
-      <c r="F133" s="9"/>
-      <c r="G133" s="9"/>
-      <c r="H133" s="9"/>
-      <c r="I133" s="9"/>
+    <row r="133" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="3">
+        <v>255</v>
+      </c>
+      <c r="B133" s="3">
+        <v>225</v>
+      </c>
+      <c r="C133" s="25" t="s">
+        <v>521</v>
+      </c>
+      <c r="D133" s="25"/>
+      <c r="E133" s="25" t="s">
+        <v>516</v>
+      </c>
+      <c r="F133" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G133" s="25">
+        <v>74</v>
+      </c>
+      <c r="H133" s="25">
+        <v>70</v>
+      </c>
+      <c r="I133" s="25">
+        <v>36</v>
+      </c>
       <c r="J133" s="17">
-        <f t="shared" si="78"/>
-        <v>0</v>
+        <f t="shared" si="63"/>
+        <v>183</v>
       </c>
       <c r="K133" s="9">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L133" s="10">
-        <f t="shared" si="79"/>
-        <v>0</v>
+        <f t="shared" si="64"/>
+        <v>255</v>
       </c>
       <c r="M133" s="11">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="N133" s="11">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="O133" s="9"/>
       <c r="P133" s="9"/>
@@ -9922,33 +10376,51 @@
       <c r="R133" s="9"/>
       <c r="S133" s="9"/>
     </row>
-    <row r="134" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C134" s="9"/>
-      <c r="D134" s="9"/>
-      <c r="E134" s="9"/>
-      <c r="F134" s="9"/>
-      <c r="G134" s="9"/>
-      <c r="H134" s="9"/>
-      <c r="I134" s="9"/>
+    <row r="134" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="3">
+        <v>230</v>
+      </c>
+      <c r="B134" s="3">
+        <v>200</v>
+      </c>
+      <c r="C134" s="26" t="s">
+        <v>527</v>
+      </c>
+      <c r="D134" s="26"/>
+      <c r="E134" s="26" t="s">
+        <v>522</v>
+      </c>
+      <c r="F134" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="G134" s="26">
+        <v>65</v>
+      </c>
+      <c r="H134" s="26">
+        <v>70</v>
+      </c>
+      <c r="I134" s="26">
+        <v>32</v>
+      </c>
       <c r="J134" s="17">
-        <f t="shared" si="78"/>
-        <v>0</v>
+        <f t="shared" si="63"/>
+        <v>165</v>
       </c>
       <c r="K134" s="9">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="L134" s="10">
-        <f t="shared" si="79"/>
-        <v>0</v>
+        <f t="shared" si="64"/>
+        <v>232.5</v>
       </c>
       <c r="M134" s="11">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N134" s="11">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O134" s="9"/>
       <c r="P134" s="9"/>
@@ -9956,33 +10428,45 @@
       <c r="R134" s="9"/>
       <c r="S134" s="9"/>
     </row>
-    <row r="135" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="9"/>
-      <c r="D135" s="9"/>
-      <c r="E135" s="9"/>
-      <c r="F135" s="9"/>
-      <c r="G135" s="9"/>
-      <c r="H135" s="9"/>
-      <c r="I135" s="9"/>
+    <row r="135" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C135" s="26" t="s">
+        <v>527</v>
+      </c>
+      <c r="D135" s="26"/>
+      <c r="E135" s="26" t="s">
+        <v>523</v>
+      </c>
+      <c r="F135" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="G135" s="26">
+        <v>67</v>
+      </c>
+      <c r="H135" s="26">
+        <v>65</v>
+      </c>
+      <c r="I135" s="26">
+        <v>32</v>
+      </c>
       <c r="J135" s="17">
-        <f t="shared" si="78"/>
-        <v>0</v>
+        <f t="shared" si="63"/>
+        <v>166.5</v>
       </c>
       <c r="K135" s="9">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L135" s="10">
-        <f t="shared" si="79"/>
-        <v>0</v>
+        <f t="shared" si="64"/>
+        <v>232.5</v>
       </c>
       <c r="M135" s="11">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N135" s="11">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O135" s="9"/>
       <c r="P135" s="9"/>
@@ -9990,33 +10474,45 @@
       <c r="R135" s="9"/>
       <c r="S135" s="9"/>
     </row>
-    <row r="136" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="9"/>
-      <c r="D136" s="9"/>
-      <c r="E136" s="9"/>
-      <c r="F136" s="9"/>
-      <c r="G136" s="9"/>
-      <c r="H136" s="9"/>
-      <c r="I136" s="9"/>
+    <row r="136" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C136" s="26" t="s">
+        <v>527</v>
+      </c>
+      <c r="D136" s="26"/>
+      <c r="E136" s="26" t="s">
+        <v>524</v>
+      </c>
+      <c r="F136" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="G136" s="26">
+        <v>70</v>
+      </c>
+      <c r="H136" s="26">
+        <v>58</v>
+      </c>
+      <c r="I136" s="26">
+        <v>32</v>
+      </c>
       <c r="J136" s="17">
-        <f t="shared" si="78"/>
-        <v>0</v>
+        <f t="shared" ref="J136:J170" si="78">(G136*$I$2)+(H136*$I$3)</f>
+        <v>169</v>
       </c>
       <c r="K136" s="9">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="L136" s="10">
-        <f t="shared" si="79"/>
-        <v>0</v>
+        <f t="shared" ref="L136:L170" si="79">J136+K136</f>
+        <v>233</v>
       </c>
       <c r="M136" s="11">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N136" s="11">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O136" s="9"/>
       <c r="P136" s="9"/>
@@ -10024,33 +10520,51 @@
       <c r="R136" s="9"/>
       <c r="S136" s="9"/>
     </row>
-    <row r="137" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C137" s="9"/>
-      <c r="D137" s="9"/>
-      <c r="E137" s="9"/>
-      <c r="F137" s="9"/>
-      <c r="G137" s="9"/>
-      <c r="H137" s="9"/>
-      <c r="I137" s="9"/>
+    <row r="137" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="3">
+        <v>240</v>
+      </c>
+      <c r="B137" s="3">
+        <v>210</v>
+      </c>
+      <c r="C137" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="D137" s="25"/>
+      <c r="E137" s="25" t="s">
+        <v>525</v>
+      </c>
+      <c r="F137" s="25" t="s">
+        <v>310</v>
+      </c>
+      <c r="G137" s="25">
+        <v>69</v>
+      </c>
+      <c r="H137" s="25">
+        <v>65</v>
+      </c>
+      <c r="I137" s="25">
+        <v>33.5</v>
+      </c>
       <c r="J137" s="17">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>170.5</v>
       </c>
       <c r="K137" s="9">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L137" s="10">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>237.5</v>
       </c>
       <c r="M137" s="11">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>209.375</v>
       </c>
       <c r="N137" s="11">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>50.25</v>
       </c>
       <c r="O137" s="9"/>
       <c r="P137" s="9"/>
@@ -10058,33 +10572,45 @@
       <c r="R137" s="9"/>
       <c r="S137" s="9"/>
     </row>
-    <row r="138" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C138" s="9"/>
-      <c r="D138" s="9"/>
-      <c r="E138" s="9"/>
-      <c r="F138" s="9"/>
-      <c r="G138" s="9"/>
-      <c r="H138" s="9"/>
-      <c r="I138" s="9"/>
+    <row r="138" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C138" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="D138" s="25"/>
+      <c r="E138" s="25" t="s">
+        <v>526</v>
+      </c>
+      <c r="F138" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="G138" s="25">
+        <v>69</v>
+      </c>
+      <c r="H138" s="25">
+        <v>65</v>
+      </c>
+      <c r="I138" s="25">
+        <v>33.5</v>
+      </c>
       <c r="J138" s="17">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>170.5</v>
       </c>
       <c r="K138" s="9">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L138" s="10">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>237.5</v>
       </c>
       <c r="M138" s="11">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>209.375</v>
       </c>
       <c r="N138" s="11">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>50.25</v>
       </c>
       <c r="O138" s="9"/>
       <c r="P138" s="9"/>
@@ -10092,33 +10618,51 @@
       <c r="R138" s="9"/>
       <c r="S138" s="9"/>
     </row>
-    <row r="139" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C139" s="9"/>
-      <c r="D139" s="9"/>
-      <c r="E139" s="9"/>
-      <c r="F139" s="9"/>
-      <c r="G139" s="9"/>
-      <c r="H139" s="9"/>
-      <c r="I139" s="9"/>
+    <row r="139" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="3">
+        <v>245</v>
+      </c>
+      <c r="B139" s="3">
+        <v>215</v>
+      </c>
+      <c r="C139" s="26" t="s">
+        <v>529</v>
+      </c>
+      <c r="D139" s="26"/>
+      <c r="E139" s="26" t="s">
+        <v>530</v>
+      </c>
+      <c r="F139" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="G139" s="26">
+        <v>68</v>
+      </c>
+      <c r="H139" s="26">
+        <v>70</v>
+      </c>
+      <c r="I139" s="26">
+        <v>33</v>
+      </c>
       <c r="J139" s="17">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="K139" s="9">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="L139" s="10">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="M139" s="11">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>206.25</v>
       </c>
       <c r="N139" s="11">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>49.5</v>
       </c>
       <c r="O139" s="9"/>
       <c r="P139" s="9"/>
@@ -10126,33 +10670,45 @@
       <c r="R139" s="9"/>
       <c r="S139" s="9"/>
     </row>
-    <row r="140" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C140" s="9"/>
-      <c r="D140" s="9"/>
-      <c r="E140" s="9"/>
-      <c r="F140" s="9"/>
-      <c r="G140" s="9"/>
-      <c r="H140" s="9"/>
-      <c r="I140" s="9"/>
+    <row r="140" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C140" s="26" t="s">
+        <v>529</v>
+      </c>
+      <c r="D140" s="26"/>
+      <c r="E140" s="26" t="s">
+        <v>531</v>
+      </c>
+      <c r="F140" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="G140" s="26">
+        <v>82</v>
+      </c>
+      <c r="H140" s="26">
+        <v>40</v>
+      </c>
+      <c r="I140" s="26">
+        <v>34</v>
+      </c>
       <c r="J140" s="17">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="K140" s="9">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="L140" s="10">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="M140" s="11">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>212.5</v>
       </c>
       <c r="N140" s="11">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="O140" s="9"/>
       <c r="P140" s="9"/>
@@ -10160,33 +10716,45 @@
       <c r="R140" s="9"/>
       <c r="S140" s="9"/>
     </row>
-    <row r="141" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C141" s="9"/>
-      <c r="D141" s="9"/>
-      <c r="E141" s="9"/>
-      <c r="F141" s="9"/>
-      <c r="G141" s="9"/>
-      <c r="H141" s="9"/>
-      <c r="I141" s="9"/>
+    <row r="141" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C141" s="26" t="s">
+        <v>529</v>
+      </c>
+      <c r="D141" s="26"/>
+      <c r="E141" s="26" t="s">
+        <v>532</v>
+      </c>
+      <c r="F141" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="G141" s="26">
+        <v>77</v>
+      </c>
+      <c r="H141" s="26">
+        <v>53</v>
+      </c>
+      <c r="I141" s="26">
+        <v>34.5</v>
+      </c>
       <c r="J141" s="17">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>180.5</v>
       </c>
       <c r="K141" s="9">
-        <f t="shared" ref="K141:K163" si="80">(G141*$I$4)+(H141*$I$5)+(I141*$I$7)</f>
-        <v>0</v>
+        <f t="shared" si="65"/>
+        <v>65</v>
       </c>
       <c r="L141" s="10">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>245.5</v>
       </c>
       <c r="M141" s="11">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>215.625</v>
       </c>
       <c r="N141" s="11">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>51.75</v>
       </c>
       <c r="O141" s="9"/>
       <c r="P141" s="9"/>
@@ -10194,33 +10762,45 @@
       <c r="R141" s="9"/>
       <c r="S141" s="9"/>
     </row>
-    <row r="142" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C142" s="9"/>
-      <c r="D142" s="9"/>
-      <c r="E142" s="9"/>
-      <c r="F142" s="9"/>
-      <c r="G142" s="9"/>
-      <c r="H142" s="9"/>
-      <c r="I142" s="9"/>
+    <row r="142" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C142" s="26" t="s">
+        <v>529</v>
+      </c>
+      <c r="D142" s="26"/>
+      <c r="E142" s="26" t="s">
+        <v>533</v>
+      </c>
+      <c r="F142" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="G142" s="26">
+        <v>75</v>
+      </c>
+      <c r="H142" s="26">
+        <v>58</v>
+      </c>
+      <c r="I142" s="26">
+        <v>34.5</v>
+      </c>
       <c r="J142" s="17">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="K142" s="9">
-        <f t="shared" si="80"/>
-        <v>0</v>
+        <f t="shared" si="65"/>
+        <v>66.5</v>
       </c>
       <c r="L142" s="10">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>245.5</v>
       </c>
       <c r="M142" s="11">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>215.625</v>
       </c>
       <c r="N142" s="11">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>51.75</v>
       </c>
       <c r="O142" s="9"/>
       <c r="P142" s="9"/>
@@ -10228,67 +10808,99 @@
       <c r="R142" s="9"/>
       <c r="S142" s="9"/>
     </row>
-    <row r="143" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C143" s="9"/>
-      <c r="D143" s="9"/>
-      <c r="E143" s="9"/>
-      <c r="F143" s="9"/>
-      <c r="G143" s="9"/>
-      <c r="H143" s="9"/>
-      <c r="I143" s="9"/>
+    <row r="143" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="3">
+        <v>255</v>
+      </c>
+      <c r="B143" s="3">
+        <v>225</v>
+      </c>
+      <c r="C143" s="25" t="s">
+        <v>537</v>
+      </c>
+      <c r="D143" s="25"/>
+      <c r="E143" s="25" t="s">
+        <v>534</v>
+      </c>
+      <c r="F143" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="G143" s="25">
+        <v>62</v>
+      </c>
+      <c r="H143" s="25">
+        <v>100</v>
+      </c>
+      <c r="I143" s="25">
+        <v>36</v>
+      </c>
       <c r="J143" s="17">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="K143" s="9">
-        <f t="shared" si="80"/>
-        <v>0</v>
+        <f t="shared" si="65"/>
+        <v>81</v>
       </c>
       <c r="L143" s="10">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="M143" s="11">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="N143" s="11">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="O143" s="9"/>
       <c r="P143" s="9"/>
-      <c r="Q143" s="9"/>
+      <c r="Q143" s="23" t="s">
+        <v>538</v>
+      </c>
       <c r="R143" s="9"/>
       <c r="S143" s="9"/>
     </row>
-    <row r="144" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C144" s="9"/>
-      <c r="D144" s="9"/>
-      <c r="E144" s="9"/>
-      <c r="F144" s="9"/>
-      <c r="G144" s="9"/>
-      <c r="H144" s="9"/>
-      <c r="I144" s="9"/>
+    <row r="144" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C144" s="25" t="s">
+        <v>537</v>
+      </c>
+      <c r="D144" s="25"/>
+      <c r="E144" s="25" t="s">
+        <v>535</v>
+      </c>
+      <c r="F144" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="G144" s="25">
+        <v>77</v>
+      </c>
+      <c r="H144" s="25">
+        <v>62</v>
+      </c>
+      <c r="I144" s="25">
+        <v>36</v>
+      </c>
       <c r="J144" s="17">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="K144" s="9">
-        <f t="shared" si="80"/>
-        <v>0</v>
+        <f t="shared" si="65"/>
+        <v>69.5</v>
       </c>
       <c r="L144" s="10">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>254.5</v>
       </c>
       <c r="M144" s="11">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="N144" s="11">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="O144" s="9"/>
       <c r="P144" s="9"/>
@@ -10296,41 +10908,57 @@
       <c r="R144" s="9"/>
       <c r="S144" s="9"/>
     </row>
-    <row r="145" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C145" s="9"/>
-      <c r="D145" s="9"/>
-      <c r="E145" s="9"/>
-      <c r="F145" s="9"/>
-      <c r="G145" s="9"/>
-      <c r="H145" s="9"/>
-      <c r="I145" s="9"/>
+    <row r="145" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C145" s="25" t="s">
+        <v>537</v>
+      </c>
+      <c r="D145" s="25"/>
+      <c r="E145" s="25" t="s">
+        <v>536</v>
+      </c>
+      <c r="F145" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="G145" s="25">
+        <v>95</v>
+      </c>
+      <c r="H145" s="25">
+        <v>18</v>
+      </c>
+      <c r="I145" s="25">
+        <v>36</v>
+      </c>
       <c r="J145" s="17">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="K145" s="9">
-        <f t="shared" si="80"/>
-        <v>0</v>
+        <f t="shared" si="65"/>
+        <v>56.5</v>
       </c>
       <c r="L145" s="10">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>255.5</v>
       </c>
       <c r="M145" s="11">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="N145" s="11">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="O145" s="9"/>
       <c r="P145" s="9"/>
-      <c r="Q145" s="9"/>
-      <c r="R145" s="9"/>
+      <c r="Q145" s="23" t="s">
+        <v>539</v>
+      </c>
+      <c r="R145" s="23" t="s">
+        <v>540</v>
+      </c>
       <c r="S145" s="9"/>
     </row>
-    <row r="146" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C146" s="9"/>
       <c r="D146" s="9"/>
       <c r="E146" s="9"/>
@@ -10343,7 +10971,7 @@
         <v>0</v>
       </c>
       <c r="K146" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L146" s="10">
@@ -10364,7 +10992,7 @@
       <c r="R146" s="9"/>
       <c r="S146" s="9"/>
     </row>
-    <row r="147" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C147" s="9"/>
       <c r="D147" s="9"/>
       <c r="E147" s="9"/>
@@ -10377,7 +11005,7 @@
         <v>0</v>
       </c>
       <c r="K147" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L147" s="10">
@@ -10398,7 +11026,7 @@
       <c r="R147" s="9"/>
       <c r="S147" s="9"/>
     </row>
-    <row r="148" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C148" s="9"/>
       <c r="D148" s="9"/>
       <c r="E148" s="9"/>
@@ -10411,7 +11039,7 @@
         <v>0</v>
       </c>
       <c r="K148" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" ref="K148:K170" si="80">(G148*$I$4)+(H148*$I$5)+(I148*$I$7)</f>
         <v>0</v>
       </c>
       <c r="L148" s="10">
@@ -10432,7 +11060,7 @@
       <c r="R148" s="9"/>
       <c r="S148" s="9"/>
     </row>
-    <row r="149" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C149" s="9"/>
       <c r="D149" s="9"/>
       <c r="E149" s="9"/>
@@ -10466,7 +11094,7 @@
       <c r="R149" s="9"/>
       <c r="S149" s="9"/>
     </row>
-    <row r="150" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C150" s="9"/>
       <c r="D150" s="9"/>
       <c r="E150" s="9"/>
@@ -10500,7 +11128,7 @@
       <c r="R150" s="9"/>
       <c r="S150" s="9"/>
     </row>
-    <row r="151" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C151" s="9"/>
       <c r="D151" s="9"/>
       <c r="E151" s="9"/>
@@ -10534,7 +11162,7 @@
       <c r="R151" s="9"/>
       <c r="S151" s="9"/>
     </row>
-    <row r="152" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C152" s="9"/>
       <c r="D152" s="9"/>
       <c r="E152" s="9"/>
@@ -10568,7 +11196,7 @@
       <c r="R152" s="9"/>
       <c r="S152" s="9"/>
     </row>
-    <row r="153" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C153" s="9"/>
       <c r="D153" s="9"/>
       <c r="E153" s="9"/>
@@ -10602,7 +11230,7 @@
       <c r="R153" s="9"/>
       <c r="S153" s="9"/>
     </row>
-    <row r="154" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C154" s="9"/>
       <c r="D154" s="9"/>
       <c r="E154" s="9"/>
@@ -10636,7 +11264,7 @@
       <c r="R154" s="9"/>
       <c r="S154" s="9"/>
     </row>
-    <row r="155" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C155" s="9"/>
       <c r="D155" s="9"/>
       <c r="E155" s="9"/>
@@ -10670,7 +11298,7 @@
       <c r="R155" s="9"/>
       <c r="S155" s="9"/>
     </row>
-    <row r="156" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C156" s="9"/>
       <c r="D156" s="9"/>
       <c r="E156" s="9"/>
@@ -10704,7 +11332,7 @@
       <c r="R156" s="9"/>
       <c r="S156" s="9"/>
     </row>
-    <row r="157" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C157" s="9"/>
       <c r="D157" s="9"/>
       <c r="E157" s="9"/>
@@ -10738,7 +11366,7 @@
       <c r="R157" s="9"/>
       <c r="S157" s="9"/>
     </row>
-    <row r="158" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C158" s="9"/>
       <c r="D158" s="9"/>
       <c r="E158" s="9"/>
@@ -10772,7 +11400,7 @@
       <c r="R158" s="9"/>
       <c r="S158" s="9"/>
     </row>
-    <row r="159" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C159" s="9"/>
       <c r="D159" s="9"/>
       <c r="E159" s="9"/>
@@ -10806,7 +11434,7 @@
       <c r="R159" s="9"/>
       <c r="S159" s="9"/>
     </row>
-    <row r="160" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C160" s="9"/>
       <c r="D160" s="9"/>
       <c r="E160" s="9"/>
@@ -10840,7 +11468,7 @@
       <c r="R160" s="9"/>
       <c r="S160" s="9"/>
     </row>
-    <row r="161" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C161" s="9"/>
       <c r="D161" s="9"/>
       <c r="E161" s="9"/>
@@ -10874,7 +11502,7 @@
       <c r="R161" s="9"/>
       <c r="S161" s="9"/>
     </row>
-    <row r="162" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C162" s="9"/>
       <c r="D162" s="9"/>
       <c r="E162" s="9"/>
@@ -10908,7 +11536,7 @@
       <c r="R162" s="9"/>
       <c r="S162" s="9"/>
     </row>
-    <row r="163" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C163" s="9"/>
       <c r="D163" s="9"/>
       <c r="E163" s="9"/>
@@ -10941,6 +11569,244 @@
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
       <c r="S163" s="9"/>
+    </row>
+    <row r="164" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C164" s="9"/>
+      <c r="D164" s="9"/>
+      <c r="E164" s="9"/>
+      <c r="F164" s="9"/>
+      <c r="G164" s="9"/>
+      <c r="H164" s="9"/>
+      <c r="I164" s="9"/>
+      <c r="J164" s="17">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="K164" s="9">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="L164" s="10">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="M164" s="11">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="N164" s="11">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="O164" s="9"/>
+      <c r="P164" s="9"/>
+      <c r="Q164" s="9"/>
+      <c r="R164" s="9"/>
+      <c r="S164" s="9"/>
+    </row>
+    <row r="165" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C165" s="9"/>
+      <c r="D165" s="9"/>
+      <c r="E165" s="9"/>
+      <c r="F165" s="9"/>
+      <c r="G165" s="9"/>
+      <c r="H165" s="9"/>
+      <c r="I165" s="9"/>
+      <c r="J165" s="17">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="K165" s="9">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="L165" s="10">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="M165" s="11">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="N165" s="11">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="O165" s="9"/>
+      <c r="P165" s="9"/>
+      <c r="Q165" s="9"/>
+      <c r="R165" s="9"/>
+      <c r="S165" s="9"/>
+    </row>
+    <row r="166" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C166" s="9"/>
+      <c r="D166" s="9"/>
+      <c r="E166" s="9"/>
+      <c r="F166" s="9"/>
+      <c r="G166" s="9"/>
+      <c r="H166" s="9"/>
+      <c r="I166" s="9"/>
+      <c r="J166" s="17">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="K166" s="9">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="L166" s="10">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="M166" s="11">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="N166" s="11">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="O166" s="9"/>
+      <c r="P166" s="9"/>
+      <c r="Q166" s="9"/>
+      <c r="R166" s="9"/>
+      <c r="S166" s="9"/>
+    </row>
+    <row r="167" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C167" s="9"/>
+      <c r="D167" s="9"/>
+      <c r="E167" s="9"/>
+      <c r="F167" s="9"/>
+      <c r="G167" s="9"/>
+      <c r="H167" s="9"/>
+      <c r="I167" s="9"/>
+      <c r="J167" s="17">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="K167" s="9">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="L167" s="10">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="M167" s="11">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="N167" s="11">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="O167" s="9"/>
+      <c r="P167" s="9"/>
+      <c r="Q167" s="9"/>
+      <c r="R167" s="9"/>
+      <c r="S167" s="9"/>
+    </row>
+    <row r="168" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C168" s="9"/>
+      <c r="D168" s="9"/>
+      <c r="E168" s="9"/>
+      <c r="F168" s="9"/>
+      <c r="G168" s="9"/>
+      <c r="H168" s="9"/>
+      <c r="I168" s="9"/>
+      <c r="J168" s="17">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="K168" s="9">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="L168" s="10">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="M168" s="11">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="N168" s="11">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="O168" s="9"/>
+      <c r="P168" s="9"/>
+      <c r="Q168" s="9"/>
+      <c r="R168" s="9"/>
+      <c r="S168" s="9"/>
+    </row>
+    <row r="169" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C169" s="9"/>
+      <c r="D169" s="9"/>
+      <c r="E169" s="9"/>
+      <c r="F169" s="9"/>
+      <c r="G169" s="9"/>
+      <c r="H169" s="9"/>
+      <c r="I169" s="9"/>
+      <c r="J169" s="17">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="K169" s="9">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="L169" s="10">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="M169" s="11">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="N169" s="11">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="O169" s="9"/>
+      <c r="P169" s="9"/>
+      <c r="Q169" s="9"/>
+      <c r="R169" s="9"/>
+      <c r="S169" s="9"/>
+    </row>
+    <row r="170" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C170" s="9"/>
+      <c r="D170" s="9"/>
+      <c r="E170" s="9"/>
+      <c r="F170" s="9"/>
+      <c r="G170" s="9"/>
+      <c r="H170" s="9"/>
+      <c r="I170" s="9"/>
+      <c r="J170" s="17">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="K170" s="9">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="L170" s="10">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="M170" s="11">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="N170" s="11">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="O170" s="9"/>
+      <c r="P170" s="9"/>
+      <c r="Q170" s="9"/>
+      <c r="R170" s="9"/>
+      <c r="S170" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -10957,9 +11823,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36FC5B27-9E4B-4195-A664-98F7198337D3}">
   <dimension ref="A1:U15"/>
-  <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.625" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3" t="s">
@@ -10978,17 +11844,17 @@
         <v>4</v>
       </c>
       <c r="J1" s="24" t="s">
+        <v>364</v>
+      </c>
+      <c r="K1" s="24" t="s">
         <v>365</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>366</v>
       </c>
       <c r="L1" s="3"/>
       <c r="M1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
@@ -11026,7 +11892,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
         <v>15</v>
@@ -11062,7 +11928,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
@@ -11090,7 +11956,7 @@
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
     </row>
-    <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
         <v>15</v>
@@ -11116,7 +11982,7 @@
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
@@ -11147,7 +12013,7 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="3" t="s">
         <v>28</v>
       </c>
@@ -11175,7 +12041,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="9" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -11201,10 +12067,10 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="U9" s="32" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
@@ -11212,10 +12078,10 @@
         <v>32</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>35</v>
@@ -11263,10 +12129,10 @@
         <v>319</v>
       </c>
       <c r="U10" s="33" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>24</v>
       </c>
@@ -11274,13 +12140,13 @@
         <v>20</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D11" s="30">
         <v>2</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F11" s="30">
         <v>6</v>
@@ -11318,17 +12184,17 @@
         <v>1</v>
       </c>
       <c r="P11" s="23" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="Q11" s="23" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="R11" s="23" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="S11" s="3"/>
     </row>
-    <row r="12" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>135</v>
       </c>
@@ -11336,13 +12202,13 @@
         <v>155</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D12" s="30">
         <v>4</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F12" s="30">
         <v>40</v>
@@ -11380,15 +12246,15 @@
         <v>1</v>
       </c>
       <c r="P12" s="23" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="Q12" s="23" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="R12" s="9"/>
       <c r="S12" s="3"/>
     </row>
-    <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>9</v>
       </c>
@@ -11396,13 +12262,13 @@
         <v>10</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D13" s="30">
         <v>1</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F13" s="30">
         <v>3</v>
@@ -11440,15 +12306,15 @@
         <v>1</v>
       </c>
       <c r="P13" s="23" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="Q13" s="23" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="R13" s="9"/>
       <c r="S13" s="3"/>
     </row>
-    <row r="14" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>14</v>
       </c>
@@ -11456,13 +12322,13 @@
         <v>15</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D14" s="30">
         <v>2</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F14" s="30">
         <v>4</v>
@@ -11500,13 +12366,13 @@
         <v>1</v>
       </c>
       <c r="P14" s="23" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="Q14" s="23"/>
       <c r="R14" s="9"/>
       <c r="S14" s="3"/>
     </row>
-    <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>50</v>
       </c>
@@ -11514,13 +12380,13 @@
         <v>60</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D15" s="30">
         <v>3</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F15" s="30">
         <v>14</v>
@@ -11558,13 +12424,13 @@
         <v>1</v>
       </c>
       <c r="P15" s="23" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q15" s="23" t="s">
+        <v>497</v>
+      </c>
+      <c r="R15" s="23" t="s">
         <v>498</v>
-      </c>
-      <c r="Q15" s="23" t="s">
-        <v>499</v>
-      </c>
-      <c r="R15" s="23" t="s">
-        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -11576,636 +12442,968 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U36"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.88671875" customWidth="1"/>
+    <col min="1" max="1" width="23.875" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="20.25" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="21.21875" customWidth="1"/>
+    <col min="9" max="9" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="K1" s="28" t="s">
-        <v>463</v>
-      </c>
       <c r="L1" s="28" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="M1" s="28" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="C2" s="5">
-        <v>52</v>
-      </c>
-      <c r="D2" s="5">
-        <v>35</v>
-      </c>
-      <c r="E2" s="5">
-        <v>29</v>
-      </c>
-      <c r="F2" s="9">
-        <v>4</v>
-      </c>
-      <c r="G2" s="9">
+        <v>461</v>
+      </c>
+      <c r="N1" s="28" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="D2" s="12">
+        <v>64</v>
+      </c>
+      <c r="E2" s="12">
+        <v>50</v>
+      </c>
+      <c r="F2" s="12">
+        <v>33</v>
+      </c>
+      <c r="I2" s="9">
+        <v>8</v>
+      </c>
+      <c r="J2" s="9">
+        <v>14</v>
+      </c>
+      <c r="K2" s="23" t="s">
+        <v>432</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>413</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>433</v>
+      </c>
+      <c r="N2" s="11"/>
+      <c r="U2" s="24"/>
+    </row>
+    <row r="3" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="26" t="s">
+        <v>499</v>
+      </c>
+      <c r="D3" s="12">
+        <v>64</v>
+      </c>
+      <c r="E3" s="12">
+        <v>50</v>
+      </c>
+      <c r="F3" s="12">
+        <v>34</v>
+      </c>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="11"/>
+      <c r="U3" s="24"/>
+    </row>
+    <row r="4" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B4" s="12"/>
+      <c r="C4" s="26" t="s">
+        <v>500</v>
+      </c>
+      <c r="D4" s="12">
+        <v>62</v>
+      </c>
+      <c r="E4" s="12">
+        <v>55</v>
+      </c>
+      <c r="F4" s="12">
+        <v>34</v>
+      </c>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="11"/>
+      <c r="U4" s="24"/>
+    </row>
+    <row r="5" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="26" t="s">
+        <v>501</v>
+      </c>
+      <c r="D5" s="12">
+        <v>68</v>
+      </c>
+      <c r="E5" s="12">
+        <v>40</v>
+      </c>
+      <c r="F5" s="12">
+        <v>33</v>
+      </c>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="11"/>
+      <c r="U5" s="24"/>
+    </row>
+    <row r="6" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="26" t="s">
+        <v>502</v>
+      </c>
+      <c r="D6" s="12">
+        <v>58</v>
+      </c>
+      <c r="E6" s="12">
+        <v>65</v>
+      </c>
+      <c r="F6" s="12">
+        <v>33</v>
+      </c>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="11"/>
+      <c r="U6" s="24"/>
+    </row>
+    <row r="7" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="D7" s="5">
+        <v>68</v>
+      </c>
+      <c r="E7" s="5">
+        <v>60</v>
+      </c>
+      <c r="F7" s="5">
+        <v>32</v>
+      </c>
+      <c r="I7" s="9">
+        <v>8</v>
+      </c>
+      <c r="J7" s="9">
+        <v>14</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>434</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="M7" s="23" t="s">
+        <v>442</v>
+      </c>
+      <c r="N7" s="11"/>
+      <c r="U7" s="24"/>
+    </row>
+    <row r="8" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D8" s="5">
+        <v>74</v>
+      </c>
+      <c r="E8" s="5">
+        <v>45</v>
+      </c>
+      <c r="F8" s="5">
+        <v>34</v>
+      </c>
+      <c r="I8" s="9">
+        <v>8</v>
+      </c>
+      <c r="J8" s="9">
+        <v>12</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>419</v>
+      </c>
+      <c r="L8" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="M8" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="N8" s="11"/>
+    </row>
+    <row r="9" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="D9" s="5">
+        <v>64</v>
+      </c>
+      <c r="E9" s="5">
+        <v>72</v>
+      </c>
+      <c r="F9" s="5">
+        <v>34</v>
+      </c>
+      <c r="I9" s="9">
+        <v>10</v>
+      </c>
+      <c r="J9" s="9">
         <v>16</v>
       </c>
-      <c r="H2" s="23" t="s">
-        <v>421</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>405</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="K2" s="24" t="s">
-        <v>332</v>
-      </c>
-      <c r="L2" s="11"/>
-      <c r="U2" s="24"/>
-    </row>
-    <row r="3" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="C3" s="5">
-        <v>46</v>
-      </c>
-      <c r="D3" s="5">
+      <c r="K9" s="23" t="s">
+        <v>436</v>
+      </c>
+      <c r="L9" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>437</v>
+      </c>
+      <c r="N9" s="11"/>
+    </row>
+    <row r="10" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="25" t="s">
+        <v>503</v>
+      </c>
+      <c r="D10" s="5">
         <v>50</v>
       </c>
-      <c r="E3" s="5">
-        <v>29</v>
-      </c>
-      <c r="F3" s="9">
-        <v>6</v>
-      </c>
-      <c r="G3" s="9">
-        <v>8</v>
-      </c>
-      <c r="H3" s="23" t="s">
-        <v>422</v>
-      </c>
-      <c r="I3" s="23" t="s">
-        <v>445</v>
-      </c>
-      <c r="J3" s="23" t="s">
-        <v>414</v>
-      </c>
-      <c r="K3" s="24"/>
-      <c r="L3" s="11"/>
-      <c r="U3" s="24"/>
-    </row>
-    <row r="4" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>462</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="C4" s="12">
-        <v>52</v>
-      </c>
-      <c r="D4" s="12">
-        <v>50</v>
-      </c>
-      <c r="E4" s="12">
-        <v>30.5</v>
-      </c>
-      <c r="F4" s="9">
-        <v>6</v>
-      </c>
-      <c r="G4" s="9">
-        <v>12</v>
-      </c>
-      <c r="H4" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="I4" s="23" t="s">
-        <v>430</v>
-      </c>
-      <c r="J4" s="23" t="s">
-        <v>431</v>
-      </c>
-      <c r="L4" s="11"/>
-      <c r="U4" s="24"/>
-    </row>
-    <row r="5" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="C5" s="5">
-        <v>58</v>
-      </c>
-      <c r="D5" s="5">
-        <v>45</v>
-      </c>
-      <c r="E5" s="5">
-        <v>31</v>
-      </c>
-      <c r="F5" s="9">
-        <v>6</v>
-      </c>
-      <c r="G5" s="9">
-        <v>12</v>
-      </c>
-      <c r="H5" s="23" t="s">
-        <v>432</v>
-      </c>
-      <c r="I5" s="23" t="s">
-        <v>364</v>
-      </c>
-      <c r="J5" s="23" t="s">
-        <v>433</v>
-      </c>
-      <c r="L5" s="11"/>
-      <c r="U5" s="24"/>
-    </row>
-    <row r="6" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>424</v>
-      </c>
-      <c r="C6" s="12">
-        <v>64</v>
-      </c>
-      <c r="D6" s="12">
-        <v>50</v>
-      </c>
-      <c r="E6" s="12">
+      <c r="E10" s="5">
+        <v>100</v>
+      </c>
+      <c r="F10" s="5">
+        <v>32</v>
+      </c>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="11"/>
+    </row>
+    <row r="11" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="25" t="s">
+        <v>504</v>
+      </c>
+      <c r="D11" s="5">
+        <v>60</v>
+      </c>
+      <c r="E11" s="5">
+        <v>80</v>
+      </c>
+      <c r="F11" s="5">
         <v>33</v>
       </c>
-      <c r="F6" s="9">
-        <v>8</v>
-      </c>
-      <c r="G6" s="9">
-        <v>14</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>434</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>414</v>
-      </c>
-      <c r="J6" s="23" t="s">
-        <v>435</v>
-      </c>
-      <c r="L6" s="11"/>
-      <c r="U6" s="24"/>
-    </row>
-    <row r="7" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="C7" s="5">
-        <v>68</v>
-      </c>
-      <c r="D7" s="5">
-        <v>60</v>
-      </c>
-      <c r="E7" s="5">
-        <v>32</v>
-      </c>
-      <c r="F7" s="9">
-        <v>8</v>
-      </c>
-      <c r="G7" s="9">
-        <v>14</v>
-      </c>
-      <c r="H7" s="23" t="s">
-        <v>436</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="J7" s="23" t="s">
-        <v>444</v>
-      </c>
-      <c r="K7" s="23" t="s">
-        <v>437</v>
-      </c>
-      <c r="L7" s="11"/>
-      <c r="U7" s="24"/>
-    </row>
-    <row r="8" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="C8" s="5">
-        <v>74</v>
-      </c>
-      <c r="D8" s="5">
-        <v>45</v>
-      </c>
-      <c r="E8" s="5">
-        <v>34</v>
-      </c>
-      <c r="F8" s="9">
-        <v>8</v>
-      </c>
-      <c r="G8" s="9">
-        <v>12</v>
-      </c>
-      <c r="H8" s="23" t="s">
-        <v>420</v>
-      </c>
-      <c r="I8" s="23" t="s">
-        <v>440</v>
-      </c>
-      <c r="J8" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="K8" s="24" t="s">
-        <v>441</v>
-      </c>
-      <c r="L8" s="11"/>
-    </row>
-    <row r="9" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="C9" s="5">
-        <v>64</v>
-      </c>
-      <c r="D9" s="5">
-        <v>72</v>
-      </c>
-      <c r="E9" s="5">
-        <v>34</v>
-      </c>
-      <c r="F9" s="9">
-        <v>10</v>
-      </c>
-      <c r="G9" s="9">
-        <v>16</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>438</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>431</v>
-      </c>
-      <c r="J9" s="23" t="s">
-        <v>439</v>
-      </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-    </row>
-    <row r="10" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>428</v>
-      </c>
-      <c r="C10" s="12">
-        <v>78</v>
-      </c>
-      <c r="D10" s="12">
-        <v>57</v>
-      </c>
-      <c r="E10" s="12">
-        <v>35</v>
-      </c>
-      <c r="F10" s="9">
-        <v>8</v>
-      </c>
-      <c r="G10" s="9">
-        <v>16</v>
-      </c>
-      <c r="H10" s="23" t="s">
-        <v>443</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>442</v>
-      </c>
-      <c r="J10" s="23" t="s">
-        <v>435</v>
-      </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-    </row>
-    <row r="11" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-    </row>
-    <row r="12" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="11"/>
+    </row>
+    <row r="12" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="25" t="s">
+        <v>505</v>
+      </c>
+      <c r="D12" s="5">
+        <v>72</v>
+      </c>
+      <c r="E12" s="5">
+        <v>50</v>
+      </c>
+      <c r="F12" s="5">
+        <v>33</v>
+      </c>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-    </row>
-    <row r="13" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="11"/>
+    </row>
+    <row r="13" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26" t="s">
+        <v>506</v>
+      </c>
+      <c r="D13" s="26">
+        <v>52</v>
+      </c>
+      <c r="E13" s="26">
+        <v>105</v>
+      </c>
+      <c r="F13" s="26">
+        <v>33</v>
+      </c>
+      <c r="I13" s="9"/>
       <c r="J13" s="9"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-    </row>
-    <row r="14" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="11"/>
+    </row>
+    <row r="14" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26" t="s">
+        <v>507</v>
+      </c>
+      <c r="D14" s="26">
+        <v>82</v>
+      </c>
+      <c r="E14" s="26">
+        <v>30</v>
+      </c>
+      <c r="F14" s="26">
+        <v>33</v>
+      </c>
+      <c r="I14" s="9"/>
       <c r="J14" s="9"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-    </row>
-    <row r="15" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="11"/>
+    </row>
+    <row r="15" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="D15" s="12">
+        <v>73</v>
+      </c>
+      <c r="E15" s="12">
+        <v>57</v>
+      </c>
+      <c r="F15" s="12">
+        <v>35</v>
+      </c>
+      <c r="I15" s="9">
+        <v>8</v>
+      </c>
+      <c r="J15" s="9">
+        <v>16</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>441</v>
+      </c>
+      <c r="L15" s="23" t="s">
+        <v>440</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>433</v>
+      </c>
+      <c r="N15" s="11"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A16" s="25" t="s">
+        <v>517</v>
+      </c>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25" t="s">
+        <v>508</v>
+      </c>
+      <c r="D16" s="25">
+        <v>84</v>
+      </c>
+      <c r="E16" s="25">
+        <v>30</v>
+      </c>
+      <c r="F16" s="25">
+        <v>33.5</v>
+      </c>
+      <c r="I16" s="9"/>
       <c r="J16" s="9"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="11"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" s="25" t="s">
+        <v>517</v>
+      </c>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25" t="s">
+        <v>509</v>
+      </c>
+      <c r="D17" s="25">
+        <v>68</v>
+      </c>
+      <c r="E17" s="25">
+        <v>70</v>
+      </c>
+      <c r="F17" s="25">
+        <v>33</v>
+      </c>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="23"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="11"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" s="25" t="s">
+        <v>517</v>
+      </c>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25" t="s">
+        <v>510</v>
+      </c>
+      <c r="D18" s="25">
+        <v>70</v>
+      </c>
+      <c r="E18" s="25">
+        <v>64</v>
+      </c>
+      <c r="F18" s="25">
+        <v>32</v>
+      </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="23"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="11"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="26" t="s">
+        <v>518</v>
+      </c>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="D19" s="12">
+        <v>71</v>
+      </c>
+      <c r="E19" s="12">
+        <v>63</v>
+      </c>
+      <c r="F19" s="12">
+        <v>33</v>
+      </c>
+      <c r="I19" s="9"/>
       <c r="J19" s="9"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="11"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="26" t="s">
+        <v>518</v>
+      </c>
       <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
+      <c r="C20" s="12" t="s">
+        <v>512</v>
+      </c>
+      <c r="D20" s="12">
+        <v>68</v>
+      </c>
+      <c r="E20" s="12">
+        <v>70</v>
+      </c>
+      <c r="F20" s="12">
+        <v>33</v>
+      </c>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="11"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" s="25" t="s">
+        <v>519</v>
+      </c>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25" t="s">
+        <v>513</v>
+      </c>
+      <c r="D21" s="25">
+        <v>50</v>
+      </c>
+      <c r="E21" s="25">
+        <v>115</v>
+      </c>
+      <c r="F21" s="25">
+        <v>33</v>
+      </c>
+      <c r="I21" s="9"/>
       <c r="J21" s="9"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="22"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="11"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="25" t="s">
+        <v>519</v>
+      </c>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25" t="s">
+        <v>514</v>
+      </c>
+      <c r="D22" s="25">
+        <v>65</v>
+      </c>
+      <c r="E22" s="25">
+        <v>77</v>
+      </c>
+      <c r="F22" s="25">
+        <v>33</v>
+      </c>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="11"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="26" t="s">
+        <v>520</v>
+      </c>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="D23" s="12">
+        <v>72</v>
+      </c>
+      <c r="E23" s="12">
+        <v>65</v>
+      </c>
+      <c r="F23" s="12">
+        <v>34.5</v>
+      </c>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="11"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" s="25" t="s">
+        <v>521</v>
+      </c>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25" t="s">
+        <v>516</v>
+      </c>
+      <c r="D24" s="25">
+        <v>74</v>
+      </c>
+      <c r="E24" s="25">
+        <v>70</v>
+      </c>
+      <c r="F24" s="25">
+        <v>36</v>
+      </c>
+      <c r="I24" s="9"/>
       <c r="J24" s="9"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="23"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="11"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" s="26" t="s">
+        <v>527</v>
+      </c>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26" t="s">
+        <v>522</v>
+      </c>
+      <c r="D25" s="26">
+        <v>65</v>
+      </c>
+      <c r="E25" s="26">
+        <v>70</v>
+      </c>
+      <c r="F25" s="26">
+        <v>32</v>
+      </c>
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="23"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="11"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="26" t="s">
+        <v>527</v>
+      </c>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26" t="s">
+        <v>523</v>
+      </c>
+      <c r="D26" s="26">
+        <v>67</v>
+      </c>
+      <c r="E26" s="26">
+        <v>65</v>
+      </c>
+      <c r="F26" s="26">
+        <v>32</v>
+      </c>
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="21"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="23"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="11"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" s="26" t="s">
+        <v>527</v>
+      </c>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26" t="s">
+        <v>524</v>
+      </c>
+      <c r="D27" s="26">
+        <v>70</v>
+      </c>
+      <c r="E27" s="26">
+        <v>58</v>
+      </c>
+      <c r="F27" s="26">
+        <v>32</v>
+      </c>
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="23"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="11"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25" t="s">
+        <v>525</v>
+      </c>
+      <c r="D28" s="25">
+        <v>69</v>
+      </c>
+      <c r="E28" s="25">
+        <v>65</v>
+      </c>
+      <c r="F28" s="25">
+        <v>33.5</v>
+      </c>
+      <c r="I28" s="9"/>
       <c r="J28" s="9"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="11"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25" t="s">
+        <v>526</v>
+      </c>
+      <c r="D29" s="25">
+        <v>69</v>
+      </c>
+      <c r="E29" s="25">
+        <v>65</v>
+      </c>
+      <c r="F29" s="25">
+        <v>33.5</v>
+      </c>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="11"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" s="26" t="s">
+        <v>529</v>
+      </c>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26" t="s">
+        <v>530</v>
+      </c>
+      <c r="D30" s="26">
+        <v>68</v>
+      </c>
+      <c r="E30" s="26">
+        <v>70</v>
+      </c>
+      <c r="F30" s="26">
+        <v>33</v>
+      </c>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="11"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A31" s="26" t="s">
+        <v>529</v>
+      </c>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26" t="s">
+        <v>531</v>
+      </c>
+      <c r="D31" s="26">
+        <v>82</v>
+      </c>
+      <c r="E31" s="26">
+        <v>40</v>
+      </c>
+      <c r="F31" s="26">
+        <v>34</v>
+      </c>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="11"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A32" s="26" t="s">
+        <v>529</v>
+      </c>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26" t="s">
+        <v>532</v>
+      </c>
+      <c r="D32" s="26">
+        <v>77</v>
+      </c>
+      <c r="E32" s="26">
+        <v>53</v>
+      </c>
+      <c r="F32" s="26">
+        <v>34.5</v>
+      </c>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="11"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33" s="26" t="s">
+        <v>529</v>
+      </c>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26" t="s">
+        <v>533</v>
+      </c>
+      <c r="D33" s="26">
+        <v>75</v>
+      </c>
+      <c r="E33" s="26">
+        <v>58</v>
+      </c>
+      <c r="F33" s="26">
+        <v>34.5</v>
+      </c>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="11"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A34" s="25" t="s">
+        <v>537</v>
+      </c>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25" t="s">
+        <v>534</v>
+      </c>
+      <c r="D34" s="25">
+        <v>62</v>
+      </c>
+      <c r="E34" s="25">
+        <v>100</v>
+      </c>
+      <c r="F34" s="25">
+        <v>36</v>
+      </c>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="23" t="s">
+        <v>538</v>
+      </c>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="11"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35" s="25" t="s">
+        <v>537</v>
+      </c>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25" t="s">
+        <v>535</v>
+      </c>
+      <c r="D35" s="25">
+        <v>77</v>
+      </c>
+      <c r="E35" s="25">
+        <v>62</v>
+      </c>
+      <c r="F35" s="25">
+        <v>36</v>
+      </c>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="11"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A36" s="25" t="s">
+        <v>537</v>
+      </c>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25" t="s">
+        <v>536</v>
+      </c>
+      <c r="D36" s="25">
+        <v>95</v>
+      </c>
+      <c r="E36" s="25">
+        <v>18</v>
+      </c>
+      <c r="F36" s="25">
+        <v>36</v>
+      </c>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="23" t="s">
+        <v>539</v>
+      </c>
+      <c r="L36" s="23" t="s">
+        <v>540</v>
+      </c>
+      <c r="M36" s="9"/>
+      <c r="N36" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -12217,7 +13415,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12227,9 +13425,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="D5:S67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="5" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:19" x14ac:dyDescent="0.2">
       <c r="F5" t="s">
         <v>256</v>
       </c>
@@ -12243,7 +13441,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="6" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:19" x14ac:dyDescent="0.2">
       <c r="F6" t="s">
         <v>260</v>
       </c>
@@ -12275,7 +13473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D7" t="s">
         <v>264</v>
       </c>
@@ -12322,7 +13520,7 @@
         <v>6.4375</v>
       </c>
     </row>
-    <row r="8" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="4:19" x14ac:dyDescent="0.2">
       <c r="E8" t="s">
         <v>28</v>
       </c>
@@ -12362,7 +13560,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="10" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D10" t="s">
         <v>265</v>
       </c>
@@ -12413,7 +13611,7 @@
         <v>1.3283417475728154</v>
       </c>
     </row>
-    <row r="11" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:19" x14ac:dyDescent="0.2">
       <c r="E11" t="s">
         <v>28</v>
       </c>
@@ -12453,7 +13651,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="12" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="4:19" x14ac:dyDescent="0.2">
       <c r="E12" t="s">
         <v>266</v>
       </c>
@@ -12489,7 +13687,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="13" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="4:19" x14ac:dyDescent="0.2">
       <c r="E13" t="s">
         <v>267</v>
       </c>
@@ -12528,7 +13726,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:19" x14ac:dyDescent="0.2">
       <c r="Q14">
         <f>Q13*$O$7</f>
         <v>12.5</v>
@@ -12538,13 +13736,13 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="15" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="4:19" x14ac:dyDescent="0.2">
       <c r="Q15">
         <f>Q13*$O$8</f>
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q17">
         <f>Q13*$O$10</f>
         <v>16.8</v>
@@ -12558,18 +13756,18 @@
         <v>1.3135698113207548</v>
       </c>
     </row>
-    <row r="18" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q18">
         <f>Q13*$O$11</f>
         <v>1.8</v>
       </c>
     </row>
-    <row r="20" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q20" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q21">
         <f>Q20*$O$7</f>
         <v>31.25</v>
@@ -12579,13 +13777,13 @@
         <v>35.9375</v>
       </c>
     </row>
-    <row r="22" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q22">
         <f>Q20*$O$8</f>
         <v>7.5</v>
       </c>
     </row>
-    <row r="24" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q24">
         <f>Q20*$O$10</f>
         <v>42</v>
@@ -12599,18 +13797,18 @@
         <v>1.2738782608695653</v>
       </c>
     </row>
-    <row r="25" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q25">
         <f>Q20*$O$11</f>
         <v>4.5</v>
       </c>
     </row>
-    <row r="27" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q27" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q28">
         <f>Q27*$O$7</f>
         <v>62.5</v>
@@ -12620,13 +13818,13 @@
         <v>81.25</v>
       </c>
     </row>
-    <row r="29" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q29">
         <f>Q27*$O$8</f>
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q31">
         <f>Q27*$O$10</f>
         <v>84</v>
@@ -12640,18 +13838,18 @@
         <v>1.2199384615384614</v>
       </c>
     </row>
-    <row r="32" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q32">
         <f>Q27*$O$11</f>
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q34" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q35">
         <f>Q34*$O$7</f>
         <v>93.75</v>
@@ -12661,13 +13859,13 @@
         <v>135.9375</v>
       </c>
     </row>
-    <row r="36" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q36">
         <f>Q34*$O$8</f>
         <v>22.5</v>
       </c>
     </row>
-    <row r="38" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q38">
         <f>Q34*$O$10</f>
         <v>126</v>
@@ -12681,18 +13879,18 @@
         <v>1.1771586206896552</v>
       </c>
     </row>
-    <row r="39" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q39">
         <f>Q34*$O$11</f>
         <v>13.5</v>
       </c>
     </row>
-    <row r="41" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q41" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q42">
         <f>Q41*$O$7</f>
         <v>125</v>
@@ -12702,13 +13900,13 @@
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q43">
         <f>Q41*$O$8</f>
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q45">
         <f>Q41*$O$10</f>
         <v>168</v>
@@ -12722,18 +13920,18 @@
         <v>1.1423999999999999</v>
       </c>
     </row>
-    <row r="46" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q46">
         <f>Q41*$O$11</f>
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q48" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q49">
         <f>Q48*$O$7</f>
         <v>156.25</v>
@@ -12743,13 +13941,13 @@
         <v>273.4375</v>
       </c>
     </row>
-    <row r="50" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q50">
         <f>Q48*$O$8</f>
         <v>37.5</v>
       </c>
     </row>
-    <row r="52" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q52">
         <f>Q48*$O$10</f>
         <v>210</v>
@@ -12763,18 +13961,18 @@
         <v>1.1135999999999999</v>
       </c>
     </row>
-    <row r="53" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q53">
         <f>Q48*$O$11</f>
         <v>22.5</v>
       </c>
     </row>
-    <row r="55" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q55" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q56">
         <f>Q55*$O$7</f>
         <v>218.75</v>
@@ -12784,13 +13982,13 @@
         <v>448.43749999999994</v>
       </c>
     </row>
-    <row r="57" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q57">
         <f>Q55*$O$8</f>
         <v>52.5</v>
       </c>
     </row>
-    <row r="59" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q59">
         <f>Q55*$O$10</f>
         <v>294</v>
@@ -12804,18 +14002,18 @@
         <v>1.0686439024390244</v>
       </c>
     </row>
-    <row r="60" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q60">
         <f>Q55*$O$11</f>
         <v>31.5</v>
       </c>
     </row>
-    <row r="62" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q62" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="63" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q63">
         <f>Q62*$O$7</f>
         <v>250</v>
@@ -12825,13 +14023,13 @@
         <v>550</v>
       </c>
     </row>
-    <row r="64" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q64">
         <f>Q62*$O$8</f>
         <v>60</v>
       </c>
     </row>
-    <row r="66" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q66">
         <f>Q62*$O$10</f>
         <v>336</v>
@@ -12845,7 +14043,7 @@
         <v>1.0507636363636363</v>
       </c>
     </row>
-    <row r="67" spans="17:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q67">
         <f>Q62*$O$11</f>
         <v>36</v>
